--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45324</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45894</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>44841</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45980</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46111</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44620</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45623</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>46253</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>46013</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46269</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>44495</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45890</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>45978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45176</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45278</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>46036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45978</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46111</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>45090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>45866</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5700,7 +5700,7 @@
         <v>45937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>45510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>45400</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45741</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45741</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45775</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44876</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44560</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44802</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44503</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44791</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>45191</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45406</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45457</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45226</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45161</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45388</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45258</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>45091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44818</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45406</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45636</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45198</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45384</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45191</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>45532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45252</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45317</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45196</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45149</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>45729</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44834</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44862</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45903</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45279</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45191</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45364</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45215</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45246</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45755</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46147</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46147</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>46147</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>46147</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>46147</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45939</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45947</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45105</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45208</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44791</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45000</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45929</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45310</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45939</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>46155</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>46155</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>46155</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45555</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>46155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45098</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45526</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45389</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>46154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46155</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46155</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44958</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45985</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45461</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44879</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>45224</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45414</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45408</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>44682</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44859</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44889</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45091</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45015</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45191</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>46043</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44910</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45758</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45555</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>46177</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>46076</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44618</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46021</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>45147</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44677</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>44791</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>46099</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>46099</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45225</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45104</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46107</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46107</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45995</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>46199</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46113</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>46113</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46113</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>46113</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45267</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>46113</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>46113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>44493</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45370</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45352</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>46245</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45461</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>46134</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>46134</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46134</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46134</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46134</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>46134</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>46134</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46134</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>44534</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45070</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>46134</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44631</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44593</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>46253</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>45158</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>46211</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>46211</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>46211</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45901</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45457</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45457</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>46211</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45145</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44550</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>46265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46265</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>46265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45714</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>46265</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46224</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>46224</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46234</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>46279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45407</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>46276</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45670</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45617</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>46281</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46239</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45414</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>46283</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>46283</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45608</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45453</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45849</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45596</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44904</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46089</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56956-2025</t>
+          <t>A 36452-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45978</v>
+        <v>46269</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>22.2</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2413,12 +2413,131 @@
         <v>6</v>
       </c>
       <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp
+Bronshjon
+Vedticka
+Linnea
+Spillkråka
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36452-2026 artfynd.xlsx", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36452-2026 karta.png", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36452-2026 georefererad karta.tif", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36452-2026 FSC-klagomål.docx", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36452-2026 FSC-klagomål mail.docx", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36452-2026 tillsynsbegäran.docx", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36452-2026 tillsynsbegäran mail.docx", "A 36452-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 36452-2026 prioriterade fågelarter.docx", "A 36452-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56956-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
         <v>15</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>15</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tretåig hackspett
@@ -2428,155 +2547,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 36452-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>10</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp
-Bronshjon
-Vedticka
-Linnea
-Spillkråka
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36452-2026 artfynd.xlsx", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36452-2026 karta.png", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36452-2026 georefererad karta.tif", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36452-2026 FSC-klagomål.docx", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36452-2026 FSC-klagomål mail.docx", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36452-2026 tillsynsbegäran.docx", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36452-2026 tillsynsbegäran mail.docx", "A 36452-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 36452-2026 prioriterade fågelarter.docx", "A 36452-2026")</f>
         <v/>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45910</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>44529</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 39837-2025</t>
+          <t>A 51036-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45891</v>
+        <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3532,17 +3532,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3571,149 +3571,149 @@
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Vårärt
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 39837-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Bårdlav
 Stuplav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 51036-2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44868</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Vårärt
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
         <v>44862</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44707</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16554-2024</t>
+          <t>A 41696-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45408</v>
+        <v>45176</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3970,13 +3970,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -3985,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4000,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4016,376 +4011,381 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
+          <t>Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 63825-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 16554-2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45408</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>Bivråk
 Blåsippa</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 16642-2024</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45408</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I33" t="n">
         <v>4</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U33" t="n">
         <v>2</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Bivråk
 Blåsippa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 41696-2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 63825-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
         <v/>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
         <v>46036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44593</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45775</v>
+        <v>45177</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5352,42 +5352,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45090</v>
+        <v>45027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5426,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5453,46 +5453,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45229</v>
+        <v>45400</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5562,42 +5562,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45866</v>
+        <v>45937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5627,13 +5627,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5667,42 +5667,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45937</v>
+        <v>45219</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,18 +5731,23 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
@@ -5756,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5768,46 +5773,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5821,10 +5830,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45177</v>
+        <v>45775</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5851,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5882,42 +5891,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31957-2024</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5931,10 +5940,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45510</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,17 +5956,17 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
@@ -5971,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5983,46 +5992,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30586-2026</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6032,14 +6041,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46210</v>
+        <v>45741</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6051,11 +6060,16 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -6092,42 +6106,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6137,14 +6151,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45219</v>
+        <v>45741</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6158,26 +6172,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
         <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6189,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6202,46 +6216,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 31957-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6255,10 +6265,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45027</v>
+        <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6271,10 +6281,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6283,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -6295,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6311,42 +6321,42 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6360,10 +6370,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45400</v>
+        <v>45090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6386,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6416,42 +6426,42 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6461,14 +6471,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45741</v>
+        <v>45866</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6480,13 +6490,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -6501,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6510,10 +6515,10 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6526,42 +6531,42 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 30586-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6571,14 +6576,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45741</v>
+        <v>46210</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6590,13 +6595,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6632,39 +6632,39 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44802</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44807</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44687</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44714</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59590-2021</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44491</v>
+        <v>44791</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7967,11 +7967,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 68887-2021</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44530</v>
+        <v>45758</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8043,13 +8043,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8092,7 +8087,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26314-2022</t>
+          <t>A 59590-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8106,10 +8101,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44735</v>
+        <v>44491</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8123,11 +8118,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8170,7 +8165,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8184,10 +8179,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44503</v>
+        <v>45184</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8200,7 +8195,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8243,7 +8238,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8257,10 +8252,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44958</v>
+        <v>45147</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8273,7 +8268,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8316,7 +8311,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 68887-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8330,10 +8325,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44791</v>
+        <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8351,7 +8346,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8394,7 +8389,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8408,10 +8403,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45191</v>
+        <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8424,7 +8419,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8467,7 +8462,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 26314-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8481,10 +8476,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45091</v>
+        <v>44735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8498,11 +8493,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8545,7 +8540,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8559,10 +8554,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45266</v>
+        <v>45091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8574,8 +8569,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8618,7 +8618,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45231</v>
+        <v>45161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45406</v>
+        <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8774,14 +8774,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45388</v>
+        <v>44845</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45457</v>
+        <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8910,7 +8910,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45226</v>
+        <v>45555</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45714</v>
+        <v>44834</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9056,7 +9056,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9070,10 +9070,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45147</v>
+        <v>45196</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9139,14 +9139,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45166</v>
+        <v>45389</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9202,7 +9202,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45161</v>
+        <v>45070</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9289,10 +9289,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45184</v>
+        <v>45406</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9348,7 +9348,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45638</v>
+        <v>45091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9377,8 +9377,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9421,7 +9426,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9435,10 +9440,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45091</v>
+        <v>45617</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9450,13 +9455,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9499,7 +9499,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9509,14 +9509,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45461</v>
+        <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9572,7 +9572,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9586,10 +9586,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45461</v>
+        <v>45414</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.2</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44818</v>
+        <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9674,13 +9674,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9723,7 +9718,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9737,10 +9732,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45406</v>
+        <v>44862</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9752,8 +9747,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9796,7 +9796,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9810,10 +9810,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44481</v>
+        <v>45406</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9869,7 +9869,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45258</v>
+        <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9942,7 +9942,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44896</v>
+        <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9971,13 +9971,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10020,7 +10015,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10030,14 +10025,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>45258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10049,13 +10044,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10098,7 +10088,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10112,10 +10102,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45182</v>
+        <v>45161</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10128,7 +10118,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10171,7 +10161,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10185,10 +10175,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45279</v>
+        <v>45457</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10200,13 +10190,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10249,7 +10234,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10263,10 +10248,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44593</v>
+        <v>45370</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10278,8 +10263,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10322,7 +10312,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10336,10 +10326,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45636</v>
+        <v>45015</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10352,7 +10342,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10395,7 +10385,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10409,10 +10399,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45714</v>
+        <v>45903</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10425,7 +10415,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10468,7 +10458,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10482,10 +10472,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44957</v>
+        <v>45279</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10497,8 +10487,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10541,7 +10536,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10555,10 +10550,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45198</v>
+        <v>45352</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10571,7 +10566,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10614,7 +10609,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10628,10 +10623,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45596</v>
+        <v>44818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10649,7 +10644,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10692,7 +10687,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10706,10 +10701,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45384</v>
+        <v>44534</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10722,7 +10717,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10765,7 +10760,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10779,10 +10774,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45461</v>
+        <v>44493</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10795,7 +10790,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10838,7 +10833,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10852,10 +10847,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44960</v>
+        <v>44889</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10867,13 +10862,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10916,7 +10906,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10926,14 +10916,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45532</v>
+        <v>45461</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10946,7 +10936,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10989,7 +10979,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11003,10 +10993,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45729</v>
+        <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11018,8 +11008,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11062,7 +11057,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11076,10 +11071,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45191</v>
+        <v>45000</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11091,8 +11086,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11135,7 +11135,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45903</v>
+        <v>45608</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11208,7 +11208,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44862</v>
+        <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11237,13 +11237,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11286,7 +11281,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11300,10 +11295,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45252</v>
+        <v>45453</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11316,7 +11311,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11359,7 +11354,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11373,10 +11368,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45317</v>
+        <v>45384</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11389,7 +11384,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11432,7 +11427,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11446,10 +11441,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45196</v>
+        <v>45408</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11461,8 +11456,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11505,7 +11505,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45149</v>
+        <v>45231</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11578,7 +11578,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11588,14 +11588,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44834</v>
+        <v>44593</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11607,8 +11607,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>38.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11651,7 +11656,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 29669-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11665,10 +11670,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46147</v>
+        <v>45825</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11678,11 +11683,6 @@
       <c r="G121" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -11729,7 +11729,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11743,10 +11743,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46147</v>
+        <v>44550</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11807,7 +11807,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21276-2026</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11817,14 +11817,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46147</v>
+        <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11836,13 +11836,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11885,7 +11880,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11899,10 +11894,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46147</v>
+        <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11914,13 +11909,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11963,7 +11953,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11977,10 +11967,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46147</v>
+        <v>45145</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11992,13 +11982,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12041,7 +12026,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12055,10 +12040,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45929</v>
+        <v>45555</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12071,7 +12056,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12114,7 +12099,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12124,14 +12109,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12144,7 +12129,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12187,7 +12172,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12201,10 +12186,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46155</v>
+        <v>44593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12216,13 +12201,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12265,7 +12245,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12275,14 +12255,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46155</v>
+        <v>45187</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12300,7 +12280,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12343,7 +12323,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12353,14 +12333,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46155</v>
+        <v>45364</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12378,7 +12358,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12421,7 +12401,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12431,14 +12411,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46155</v>
+        <v>45953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12456,7 +12436,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12499,7 +12479,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12513,10 +12493,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45526</v>
+        <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12528,13 +12508,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12577,7 +12552,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 29669-2025</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12591,10 +12566,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45825</v>
+        <v>45158</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12607,7 +12582,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12650,7 +12625,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12664,10 +12639,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46154</v>
+        <v>45191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12679,13 +12654,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12728,7 +12698,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12738,14 +12708,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45939</v>
+        <v>45226</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12758,7 +12728,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12801,7 +12771,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12815,10 +12785,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45947</v>
+        <v>45191</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12831,7 +12801,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12874,7 +12844,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12888,10 +12858,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46155</v>
+        <v>44677</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12903,13 +12873,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12952,7 +12917,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12966,10 +12931,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46155</v>
+        <v>45965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12981,13 +12946,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13030,7 +12990,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13040,14 +13000,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45953</v>
+        <v>45317</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13059,13 +13019,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13108,7 +13063,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13122,10 +13077,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45279</v>
+        <v>45215</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13137,13 +13092,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13186,7 +13136,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13200,10 +13150,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45191</v>
+        <v>45149</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13216,7 +13166,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13259,7 +13209,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13269,14 +13219,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45364</v>
+        <v>45714</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13288,13 +13238,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13337,7 +13282,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13351,10 +13296,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45965</v>
+        <v>45198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13367,7 +13312,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13410,7 +13355,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13424,10 +13369,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45215</v>
+        <v>45714</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13440,7 +13385,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13483,7 +13428,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13497,10 +13442,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45246</v>
+        <v>44682</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13512,13 +13457,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13561,7 +13501,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13575,10 +13515,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45755</v>
+        <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13591,7 +13531,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13634,7 +13574,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13648,10 +13588,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45985</v>
+        <v>45457</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13664,7 +13604,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13707,7 +13647,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13721,10 +13661,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45105</v>
+        <v>45457</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13737,7 +13677,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13780,7 +13720,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13794,10 +13734,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45208</v>
+        <v>45740</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13810,7 +13750,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13853,7 +13793,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13867,10 +13807,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44791</v>
+        <v>45166</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13882,13 +13822,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13931,7 +13866,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13945,10 +13880,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45161</v>
+        <v>45994</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13961,7 +13896,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14004,7 +13939,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14018,10 +13953,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45000</v>
+        <v>45994</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14033,13 +13968,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14082,7 +14012,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14096,10 +14026,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45994</v>
+        <v>45461</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14112,7 +14042,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14155,7 +14085,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14169,10 +14099,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45994</v>
+        <v>45267</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14185,7 +14115,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14228,7 +14158,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14242,10 +14172,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45740</v>
+        <v>46034</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14258,7 +14188,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14301,7 +14231,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14315,10 +14245,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45310</v>
+        <v>44503</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14331,7 +14261,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14374,7 +14304,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14388,10 +14318,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44845</v>
+        <v>46043</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14404,7 +14334,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14447,7 +14377,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14461,10 +14391,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45555</v>
+        <v>45755</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14477,7 +14407,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14520,7 +14450,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14534,10 +14464,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45098</v>
+        <v>46283</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14549,8 +14479,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14593,7 +14528,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14603,14 +14538,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45389</v>
+        <v>45091</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14622,8 +14557,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14666,7 +14606,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14680,10 +14620,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46177</v>
+        <v>44896</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14695,8 +14635,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14739,7 +14684,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14753,10 +14698,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44958</v>
+        <v>45208</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14769,7 +14714,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14812,7 +14757,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14826,10 +14771,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46034</v>
+        <v>45461</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14842,7 +14787,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14885,7 +14830,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14899,10 +14844,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45461</v>
+        <v>46283</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14914,8 +14859,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14958,7 +14908,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14972,10 +14922,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46043</v>
+        <v>46283</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14987,8 +14937,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15031,7 +14986,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15041,14 +14996,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44879</v>
+        <v>46245</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15061,7 +15016,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15104,7 +15059,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15118,10 +15073,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45224</v>
+        <v>46076</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15133,8 +15088,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15177,7 +15137,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15191,10 +15151,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45414</v>
+        <v>44791</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15206,8 +15166,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15250,7 +15215,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15264,10 +15229,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45408</v>
+        <v>46021</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15279,13 +15244,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15328,7 +15288,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15342,10 +15302,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44682</v>
+        <v>46099</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15358,7 +15318,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15401,7 +15361,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15415,10 +15375,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45995</v>
+        <v>45849</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15430,8 +15390,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15474,7 +15439,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15488,10 +15453,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46076</v>
+        <v>46099</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15503,13 +15468,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15552,7 +15512,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15566,10 +15526,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44859</v>
+        <v>45224</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15582,7 +15542,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15625,7 +15585,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15639,10 +15599,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46199</v>
+        <v>44960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15654,8 +15614,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15698,7 +15663,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15712,10 +15677,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46021</v>
+        <v>46107</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15728,7 +15693,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15771,7 +15736,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15785,10 +15750,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44889</v>
+        <v>45147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15801,7 +15766,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.9</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15844,7 +15809,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15858,10 +15823,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15874,7 +15839,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15917,7 +15882,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15931,10 +15896,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15947,7 +15912,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15990,7 +15955,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16004,10 +15969,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45091</v>
+        <v>46113</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16021,11 +15986,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16068,7 +16033,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16082,10 +16047,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45015</v>
+        <v>46113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16095,6 +16060,11 @@
       <c r="G180" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -16141,7 +16111,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16155,10 +16125,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45191</v>
+        <v>46113</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16170,8 +16140,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16214,7 +16189,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16228,10 +16203,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16243,8 +16218,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16287,7 +16267,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16301,10 +16281,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44910</v>
+        <v>46113</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16316,8 +16296,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16360,7 +16345,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16374,10 +16359,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16389,8 +16374,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16433,7 +16423,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16447,10 +16437,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45758</v>
+        <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16462,8 +16452,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16506,7 +16501,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16520,10 +16515,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46107</v>
+        <v>45461</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16536,7 +16531,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16579,7 +16574,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16593,10 +16588,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46113</v>
+        <v>45266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16608,13 +16603,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16657,7 +16647,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16671,10 +16661,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46113</v>
+        <v>45414</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16686,13 +16676,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16735,7 +16720,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16749,10 +16734,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46113</v>
+        <v>45596</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16770,7 +16755,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16813,7 +16798,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16827,10 +16812,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16848,7 +16833,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16891,7 +16876,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16905,10 +16890,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16926,7 +16911,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16969,7 +16954,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16983,10 +16968,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17004,7 +16989,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17047,7 +17032,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17061,10 +17046,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17082,7 +17067,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17125,7 +17110,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17139,10 +17124,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45555</v>
+        <v>46134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17154,8 +17139,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17198,7 +17188,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17215,7 +17205,7 @@
         <v>46134</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17233,7 +17223,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17276,7 +17266,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17290,10 +17280,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46134</v>
+        <v>45638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17305,13 +17295,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17371,7 +17356,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17449,7 +17434,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17510,7 +17495,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17527,7 +17512,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17545,7 +17530,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17588,7 +17573,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17602,10 +17587,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46134</v>
+        <v>44958</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17617,13 +17602,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17666,7 +17646,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17680,10 +17660,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46134</v>
+        <v>45523</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17695,13 +17675,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17744,7 +17719,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17758,10 +17733,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46134</v>
+        <v>45105</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17773,13 +17748,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17822,7 +17792,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17836,10 +17806,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46134</v>
+        <v>45461</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17851,13 +17821,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17900,7 +17865,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17914,10 +17879,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44618</v>
+        <v>45182</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17973,7 +17938,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17987,10 +17952,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45523</v>
+        <v>45191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18003,7 +17968,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18046,7 +18011,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18060,10 +18025,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46253</v>
+        <v>44910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18076,7 +18041,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18119,7 +18084,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18133,10 +18098,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45147</v>
+        <v>44631</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18148,8 +18113,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18192,7 +18162,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 8936-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18206,10 +18176,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44677</v>
+        <v>45714</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18222,7 +18192,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18265,7 +18235,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18279,10 +18249,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46211</v>
+        <v>45098</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18295,7 +18265,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18338,7 +18308,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18348,14 +18318,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46211</v>
+        <v>45388</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18368,7 +18338,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18411,7 +18381,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18425,10 +18395,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46211</v>
+        <v>45279</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18440,8 +18410,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18484,7 +18459,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18498,10 +18473,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45901</v>
+        <v>45252</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18514,7 +18489,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18557,7 +18532,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18571,10 +18546,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44791</v>
+        <v>45636</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18587,7 +18562,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18630,7 +18605,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18644,10 +18619,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46211</v>
+        <v>45729</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18660,7 +18635,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18703,7 +18678,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18717,10 +18692,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45225</v>
+        <v>44618</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18733,7 +18708,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18776,7 +18751,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18786,14 +18761,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45104</v>
+        <v>45532</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18806,7 +18781,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18849,7 +18824,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18863,10 +18838,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45267</v>
+        <v>46147</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18878,8 +18853,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18922,7 +18902,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18936,10 +18916,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18957,7 +18937,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19000,7 +18980,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19014,10 +18994,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46265</v>
+        <v>45310</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19029,13 +19009,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19078,7 +19053,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19092,10 +19067,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44493</v>
+        <v>46147</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19107,8 +19082,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19151,7 +19131,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19165,10 +19145,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19186,7 +19166,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19229,7 +19209,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 21276-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19243,10 +19223,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19264,7 +19244,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19307,7 +19287,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19317,14 +19297,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45370</v>
+        <v>45939</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19336,13 +19316,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19385,7 +19360,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19399,10 +19374,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45352</v>
+        <v>46154</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19414,8 +19389,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19458,7 +19438,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 16281-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19472,10 +19452,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46265</v>
+        <v>45407</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19487,13 +19467,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19536,7 +19511,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19550,10 +19525,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45461</v>
+        <v>46155</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19565,8 +19540,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19609,7 +19589,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31579-2026</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19623,10 +19603,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46224</v>
+        <v>45526</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19638,8 +19618,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19682,7 +19667,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19696,10 +19681,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46224</v>
+        <v>46155</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19711,8 +19696,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19755,7 +19745,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19769,10 +19759,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44534</v>
+        <v>46155</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19784,8 +19774,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19828,7 +19823,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19842,10 +19837,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45070</v>
+        <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19858,7 +19853,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19901,7 +19896,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19915,10 +19910,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46268</v>
+        <v>46155</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19930,8 +19925,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19974,7 +19974,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19988,10 +19988,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44631</v>
+        <v>46155</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20052,7 +20052,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20062,14 +20062,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44593</v>
+        <v>46155</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20083,11 +20083,11 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>38.4</v>
+        <v>5.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20130,7 +20130,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20144,10 +20144,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46234</v>
+        <v>46177</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20203,7 +20203,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20217,10 +20217,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46279</v>
+        <v>45995</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20276,7 +20276,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20290,10 +20290,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46276</v>
+        <v>46199</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20305,13 +20305,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20354,7 +20349,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20368,10 +20363,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45158</v>
+        <v>46211</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20384,7 +20379,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20427,7 +20422,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20441,10 +20436,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46281</v>
+        <v>46211</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20456,13 +20451,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20505,7 +20495,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20519,10 +20509,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20534,13 +20524,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20583,7 +20568,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20597,10 +20582,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45457</v>
+        <v>45901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20613,7 +20598,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20656,7 +20641,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20670,10 +20655,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45457</v>
+        <v>46211</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20686,7 +20671,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20729,7 +20714,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20743,10 +20728,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46283</v>
+        <v>46253</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20758,13 +20743,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20807,7 +20787,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20821,10 +20801,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46283</v>
+        <v>46265</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20842,7 +20822,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20885,7 +20865,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20899,10 +20879,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46283</v>
+        <v>46265</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20920,7 +20900,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20963,7 +20943,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20977,10 +20957,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45145</v>
+        <v>46265</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20992,8 +20972,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21036,7 +21021,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21050,10 +21035,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44550</v>
+        <v>46265</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21071,7 +21056,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21114,7 +21099,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21128,10 +21113,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21141,6 +21126,11 @@
       <c r="G247" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I247" t="n">
@@ -21187,7 +21177,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 8936-2025</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21201,10 +21191,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45714</v>
+        <v>46268</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21260,7 +21250,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 16281-2024</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21274,10 +21264,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45407</v>
+        <v>46224</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21290,7 +21280,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21333,7 +21323,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 31579-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21347,10 +21337,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45670</v>
+        <v>46224</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21363,7 +21353,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21406,7 +21396,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21420,10 +21410,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45617</v>
+        <v>46276</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21435,8 +21425,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21479,7 +21474,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21493,10 +21488,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45414</v>
+        <v>46279</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21509,7 +21504,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21552,7 +21547,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21566,10 +21561,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45608</v>
+        <v>46234</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21582,7 +21577,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21625,7 +21620,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21639,10 +21634,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45453</v>
+        <v>46281</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21654,8 +21649,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21698,7 +21698,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21712,10 +21712,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45849</v>
+        <v>46239</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21793,7 +21793,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44904</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>46089</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 36452-2026</t>
+          <t>A 56956-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46269</v>
+        <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2376,20 +2376,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>22.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2413,12 +2413,131 @@
         <v>6</v>
       </c>
       <c r="T16" t="n">
+        <v>15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tretåig hackspett
+Bronshjon
+Gullgröppa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 36452-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
         <v>10</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Svartvit taggsvamp
 Bronshjon
@@ -2428,155 +2547,36 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36452-2026 artfynd.xlsx", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36452-2026 karta.png", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36452-2026 georefererad karta.tif", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36452-2026 FSC-klagomål.docx", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36452-2026 FSC-klagomål mail.docx", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36452-2026 tillsynsbegäran.docx", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36452-2026 tillsynsbegäran mail.docx", "A 36452-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 36452-2026 prioriterade fågelarter.docx", "A 36452-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 56956-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>15</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tretåig hackspett
-Bronshjon
-Gullgröppa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
         <v/>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45890</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45960</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46013</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45978</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45910</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>44529</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 51036-2022</t>
+          <t>A 39837-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44868</v>
+        <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3571,149 +3571,149 @@
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Stuplav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 51036-2022</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44868</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Vårärt
 Blåmossa</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 39837-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45891</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Stuplav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
         <v/>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
         <v>44862</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44707</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41696-2023</t>
+          <t>A 16554-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45176</v>
+        <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3970,8 +3970,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -3980,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3995,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4011,381 +4016,376 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 16642-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45408</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 41696-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>Järpe
 Spillkråka</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 63825-2023</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
         <v>45278</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="E33" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I33" t="n">
         <v>1.4</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Skogsödla</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 16554-2024</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 16642-2024</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
         <v/>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
         <v>46036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44593</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45177</v>
+        <v>45775</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5352,42 +5352,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45027</v>
+        <v>45090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5426,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5453,46 +5453,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45400</v>
+        <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5562,42 +5562,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45937</v>
+        <v>45866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5627,13 +5627,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5667,42 +5667,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45219</v>
+        <v>45937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,22 +5731,17 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5761,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5773,50 +5768,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5830,10 +5821,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45775</v>
+        <v>45177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5851,7 +5842,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5891,42 +5882,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 31957-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5940,10 +5931,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>45510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5956,16 +5947,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5980,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5992,46 +5983,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6041,14 +6032,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45741</v>
+        <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6062,11 +6053,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6075,13 +6066,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6093,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6102,46 +6093,50 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6151,14 +6146,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45741</v>
+        <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6170,13 +6165,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6188,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6216,42 +6206,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31957-2024</t>
+          <t>A 30586-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6265,10 +6255,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45510</v>
+        <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6281,23 +6271,23 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
@@ -6305,10 +6295,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6317,46 +6307,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6370,10 +6360,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45090</v>
+        <v>45400</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6386,7 +6376,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6426,42 +6416,42 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6471,14 +6461,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45866</v>
+        <v>45741</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,8 +6480,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -6506,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6515,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6531,42 +6526,42 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30586-2026</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6576,14 +6571,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46210</v>
+        <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,8 +6590,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6632,39 +6632,39 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>44802</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44807</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44687</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44714</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>44841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 59590-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44791</v>
+        <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7967,11 +7967,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 68887-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45758</v>
+        <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8043,8 +8043,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8087,7 +8092,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59590-2021</t>
+          <t>A 26314-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8101,10 +8106,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44491</v>
+        <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8118,11 +8123,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8165,7 +8170,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8179,10 +8184,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45184</v>
+        <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8195,7 +8200,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8238,7 +8243,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8252,10 +8257,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45147</v>
+        <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8267,8 +8272,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8311,7 +8321,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 68887-2021</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8325,10 +8335,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44530</v>
+        <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8340,13 +8350,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8389,7 +8394,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8403,10 +8408,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45225</v>
+        <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8419,7 +8424,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8462,7 +8467,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26314-2022</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8476,10 +8481,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44735</v>
+        <v>45266</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8491,13 +8496,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8554,10 +8554,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45091</v>
+        <v>45406</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8569,13 +8569,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8618,7 +8613,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8632,10 +8627,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45161</v>
+        <v>45091</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8647,8 +8642,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8701,14 +8701,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44791</v>
+        <v>45388</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44845</v>
+        <v>45457</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45670</v>
+        <v>45226</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8910,7 +8910,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45555</v>
+        <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8983,7 +8983,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44834</v>
+        <v>45147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9056,7 +9056,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9070,10 +9070,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45196</v>
+        <v>45166</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9139,14 +9139,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45389</v>
+        <v>45161</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9202,7 +9202,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45070</v>
+        <v>45184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9289,10 +9289,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45406</v>
+        <v>45638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9348,7 +9348,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45091</v>
+        <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9377,13 +9377,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9426,7 +9421,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9440,10 +9435,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45617</v>
+        <v>45091</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9455,8 +9450,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9499,7 +9499,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9509,14 +9509,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44879</v>
+        <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9572,7 +9572,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9586,10 +9586,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45414</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>12.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9645,7 +9645,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44481</v>
+        <v>44818</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9674,8 +9674,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9718,7 +9723,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9732,10 +9737,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44862</v>
+        <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9747,13 +9752,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9796,7 +9796,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9813,7 +9813,7 @@
         <v>45406</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9869,7 +9869,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44958</v>
+        <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9942,7 +9942,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45104</v>
+        <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9971,8 +9971,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10015,7 +10020,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10025,14 +10030,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45258</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10044,8 +10049,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10088,7 +10098,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10102,10 +10112,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45161</v>
+        <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10118,7 +10128,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10161,7 +10171,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10175,10 +10185,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45457</v>
+        <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10190,8 +10200,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10234,7 +10249,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10248,10 +10263,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45370</v>
+        <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10263,13 +10278,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10312,7 +10322,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10326,10 +10336,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45015</v>
+        <v>45636</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10342,7 +10352,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10385,7 +10395,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10399,10 +10409,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45903</v>
+        <v>45714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10415,7 +10425,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10458,7 +10468,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10472,10 +10482,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45279</v>
+        <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10487,13 +10497,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10536,7 +10541,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10550,10 +10555,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45352</v>
+        <v>45198</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10566,7 +10571,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10609,7 +10614,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10623,10 +10628,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44818</v>
+        <v>46134</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10644,7 +10649,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10687,7 +10692,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10701,10 +10706,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44534</v>
+        <v>45596</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10714,6 +10719,11 @@
       <c r="G108" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -10760,7 +10770,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10774,10 +10784,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44493</v>
+        <v>45384</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10790,7 +10800,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10833,7 +10843,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10847,10 +10857,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44889</v>
+        <v>45461</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10906,7 +10916,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10920,10 +10930,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45461</v>
+        <v>44960</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10935,8 +10945,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10979,7 +10994,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10993,10 +11008,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45246</v>
+        <v>45903</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11008,13 +11023,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11057,7 +11067,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11071,10 +11081,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45000</v>
+        <v>45191</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11086,13 +11096,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11135,7 +11140,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11149,10 +11154,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45608</v>
+        <v>44862</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11164,8 +11169,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11208,7 +11218,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11222,10 +11232,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45191</v>
+        <v>45252</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11238,7 +11248,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11281,7 +11291,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11295,10 +11305,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45453</v>
+        <v>45317</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11311,7 +11321,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11354,7 +11364,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11368,10 +11378,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45384</v>
+        <v>45196</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11384,7 +11394,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11427,7 +11437,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11441,10 +11451,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45408</v>
+        <v>45149</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11456,13 +11466,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11505,7 +11510,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11519,10 +11524,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45231</v>
+        <v>44834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11535,7 +11540,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11578,7 +11583,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11592,10 +11597,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44593</v>
+        <v>45532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11607,13 +11612,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>38.4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11656,7 +11656,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29669-2025</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11670,10 +11670,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45825</v>
+        <v>45729</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11729,7 +11729,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 29669-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11743,10 +11743,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44550</v>
+        <v>45825</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11758,13 +11758,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11824,7 +11819,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11880,7 +11875,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11894,10 +11889,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44957</v>
+        <v>45947</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11910,7 +11905,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11953,7 +11948,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11967,10 +11962,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45145</v>
+        <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11982,8 +11977,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12026,7 +12026,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12040,10 +12040,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45555</v>
+        <v>45191</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12099,7 +12099,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12109,14 +12109,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45947</v>
+        <v>45953</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12128,8 +12128,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12172,7 +12177,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12182,14 +12187,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44593</v>
+        <v>45364</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12201,8 +12206,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12245,7 +12255,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12255,14 +12265,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45187</v>
+        <v>45215</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12274,13 +12284,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12323,7 +12328,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12333,14 +12338,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45364</v>
+        <v>45246</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12358,7 +12363,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12401,7 +12406,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12411,14 +12416,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45953</v>
+        <v>45755</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12430,13 +12435,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12479,7 +12479,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44859</v>
+        <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12552,7 +12552,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45158</v>
+        <v>45105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12625,7 +12625,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12639,10 +12639,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45191</v>
+        <v>45208</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12698,7 +12698,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45226</v>
+        <v>44791</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12727,8 +12727,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12771,7 +12776,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12785,10 +12790,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45191</v>
+        <v>45161</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12801,7 +12806,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12844,7 +12849,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12858,10 +12863,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44677</v>
+        <v>45000</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12873,8 +12878,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12917,7 +12927,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12931,10 +12941,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45965</v>
+        <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12947,7 +12957,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12990,7 +13000,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13004,10 +13014,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45317</v>
+        <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13020,7 +13030,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13063,7 +13073,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13077,10 +13087,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45215</v>
+        <v>46147</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13092,8 +13102,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13136,7 +13151,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13150,10 +13165,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45149</v>
+        <v>46147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13165,8 +13180,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13209,7 +13229,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 21276-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13223,10 +13243,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45714</v>
+        <v>46147</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13238,8 +13258,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13282,7 +13307,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13296,10 +13321,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45198</v>
+        <v>46147</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13311,8 +13336,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13355,7 +13385,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13369,10 +13399,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45714</v>
+        <v>46147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13384,8 +13414,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13428,7 +13463,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13442,10 +13477,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44682</v>
+        <v>45994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13458,7 +13493,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13501,7 +13536,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13515,10 +13550,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13531,7 +13566,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13574,7 +13609,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13588,10 +13623,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45457</v>
+        <v>45929</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13604,7 +13639,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13647,7 +13682,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13657,14 +13692,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45457</v>
+        <v>45939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13677,7 +13712,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13720,7 +13755,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13734,10 +13769,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45740</v>
+        <v>46155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13747,6 +13782,11 @@
       <c r="G149" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -13793,7 +13833,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13807,10 +13847,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45166</v>
+        <v>46155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13820,6 +13860,11 @@
       <c r="G150" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -13866,7 +13911,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13880,10 +13925,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45994</v>
+        <v>46155</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13895,8 +13940,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13939,7 +13989,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13953,10 +14003,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45994</v>
+        <v>45310</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13969,7 +14019,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14012,7 +14062,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14026,10 +14076,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45461</v>
+        <v>46155</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14041,8 +14091,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>9</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14085,7 +14140,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14099,10 +14154,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45267</v>
+        <v>44845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14115,7 +14170,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14158,7 +14213,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14172,10 +14227,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46034</v>
+        <v>45526</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14187,8 +14242,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14231,7 +14291,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14245,10 +14305,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44503</v>
+        <v>45555</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14261,7 +14321,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14304,7 +14364,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14318,10 +14378,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46043</v>
+        <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14333,8 +14393,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14377,7 +14442,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14391,10 +14456,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45755</v>
+        <v>46155</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14406,8 +14471,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14450,7 +14520,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14464,10 +14534,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46283</v>
+        <v>46155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14485,7 +14555,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14528,7 +14598,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14542,10 +14612,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45091</v>
+        <v>45098</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14557,13 +14627,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14606,7 +14671,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14616,14 +14681,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44896</v>
+        <v>45389</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14635,13 +14700,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14684,7 +14744,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14698,10 +14758,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45208</v>
+        <v>44958</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14714,7 +14774,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14757,7 +14817,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14774,7 +14834,7 @@
         <v>45461</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14787,7 +14847,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14830,7 +14890,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14844,10 +14904,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46283</v>
+        <v>46034</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14859,13 +14919,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14908,7 +14963,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14918,14 +14973,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46283</v>
+        <v>44879</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14937,13 +14992,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14986,7 +15036,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15000,10 +15050,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46245</v>
+        <v>46043</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15016,7 +15066,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15059,7 +15109,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15073,10 +15123,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46076</v>
+        <v>45224</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15088,13 +15138,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15137,7 +15182,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15151,10 +15196,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44791</v>
+        <v>45414</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15166,13 +15211,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15215,7 +15255,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15229,10 +15269,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46021</v>
+        <v>45408</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15244,8 +15284,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15288,7 +15333,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15302,10 +15347,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46099</v>
+        <v>44682</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15318,7 +15363,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15361,7 +15406,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15375,10 +15420,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45849</v>
+        <v>44859</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15390,13 +15435,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15439,7 +15479,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15453,10 +15493,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46099</v>
+        <v>44889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15469,7 +15509,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15512,7 +15552,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15526,10 +15566,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45224</v>
+        <v>46076</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15541,8 +15581,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15585,7 +15630,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15599,10 +15644,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44960</v>
+        <v>46021</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15614,13 +15659,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15663,7 +15703,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15677,10 +15717,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46107</v>
+        <v>45091</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15692,8 +15732,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15736,7 +15781,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15750,10 +15795,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45147</v>
+        <v>45015</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15766,7 +15811,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15809,7 +15854,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15823,10 +15868,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46107</v>
+        <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15839,7 +15884,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15882,7 +15927,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15896,10 +15941,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46107</v>
+        <v>44910</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15912,7 +15957,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15955,7 +16000,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15969,10 +16014,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46113</v>
+        <v>45758</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15984,13 +16029,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16033,7 +16073,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16047,10 +16087,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16062,13 +16102,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16111,7 +16146,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16125,10 +16160,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16140,13 +16175,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16189,7 +16219,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16203,10 +16233,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46113</v>
+        <v>46177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16218,13 +16248,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16267,7 +16292,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16281,10 +16306,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16296,13 +16321,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16345,7 +16365,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16359,10 +16379,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16374,13 +16394,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16423,7 +16438,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16437,10 +16452,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16452,13 +16467,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16501,7 +16511,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16515,10 +16525,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45461</v>
+        <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16531,7 +16541,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>12.2</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16574,7 +16584,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16588,10 +16598,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45266</v>
+        <v>46113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16603,8 +16613,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16647,7 +16662,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16661,10 +16676,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45414</v>
+        <v>46113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16676,8 +16691,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16720,7 +16740,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16734,10 +16754,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45596</v>
+        <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16755,7 +16775,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16798,7 +16818,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16812,10 +16832,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16833,7 +16853,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16876,7 +16896,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16890,10 +16910,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16911,7 +16931,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16954,7 +16974,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16968,10 +16988,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16989,7 +17009,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17032,7 +17052,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17046,10 +17066,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17067,7 +17087,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17110,7 +17130,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17124,10 +17144,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46134</v>
+        <v>44618</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17137,11 +17157,6 @@
       <c r="G194" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -17188,7 +17203,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17202,10 +17217,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46134</v>
+        <v>45523</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17217,13 +17232,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17266,7 +17276,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17280,10 +17290,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45638</v>
+        <v>46134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17295,8 +17305,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17339,7 +17354,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17356,7 +17371,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17374,7 +17389,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17417,7 +17432,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 19510-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17434,7 +17449,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17452,7 +17467,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17495,7 +17510,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 19512-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17512,7 +17527,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17530,7 +17545,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17573,7 +17588,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17587,10 +17602,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44958</v>
+        <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17602,8 +17617,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17646,7 +17666,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17660,10 +17680,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45523</v>
+        <v>46134</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17675,8 +17695,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17719,7 +17744,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17733,10 +17758,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45105</v>
+        <v>46134</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17748,8 +17773,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17792,7 +17822,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17806,10 +17836,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45461</v>
+        <v>46134</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17821,8 +17851,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17865,7 +17900,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17879,10 +17914,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45182</v>
+        <v>45147</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17895,7 +17930,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17938,7 +17973,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17952,10 +17987,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45191</v>
+        <v>44677</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17968,7 +18003,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18011,7 +18046,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18025,10 +18060,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44910</v>
+        <v>45995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18041,7 +18076,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18084,7 +18119,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18098,10 +18133,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44631</v>
+        <v>46199</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18113,13 +18148,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18162,7 +18192,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 8936-2025</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18176,10 +18206,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45714</v>
+        <v>44791</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18192,7 +18222,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18235,7 +18265,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18249,10 +18279,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45098</v>
+        <v>45225</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18265,7 +18295,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18308,7 +18338,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18318,14 +18348,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45388</v>
+        <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18338,7 +18368,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18381,7 +18411,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18395,10 +18425,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45279</v>
+        <v>45267</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18410,13 +18440,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18459,7 +18484,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18473,10 +18498,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45252</v>
+        <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18489,7 +18514,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18532,7 +18557,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18546,10 +18571,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45636</v>
+        <v>44493</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18562,7 +18587,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18605,7 +18630,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18619,10 +18644,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45729</v>
+        <v>45370</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18634,8 +18659,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18678,7 +18708,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18692,10 +18722,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44618</v>
+        <v>45352</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18708,7 +18738,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18751,7 +18781,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18761,14 +18791,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45532</v>
+        <v>45461</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18781,7 +18811,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18824,7 +18854,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18838,10 +18868,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46147</v>
+        <v>46211</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18853,13 +18883,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18902,7 +18927,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18916,10 +18941,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46147</v>
+        <v>46211</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18931,13 +18956,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18980,7 +19000,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18994,10 +19014,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45310</v>
+        <v>46211</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19010,7 +19030,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19053,7 +19073,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19067,10 +19087,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46147</v>
+        <v>45901</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19082,13 +19102,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19131,7 +19146,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19145,10 +19160,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46147</v>
+        <v>46211</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19160,13 +19175,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19209,7 +19219,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21276-2026</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19223,10 +19233,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46147</v>
+        <v>44534</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19236,11 +19246,6 @@
       <c r="G222" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -19287,7 +19292,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19297,14 +19302,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45939</v>
+        <v>45070</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19317,7 +19322,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19360,7 +19365,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19374,10 +19379,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46154</v>
+        <v>44631</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19395,7 +19400,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19438,7 +19443,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16281-2024</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19452,10 +19457,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45407</v>
+        <v>46265</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19467,8 +19472,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19511,7 +19521,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19521,14 +19531,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46155</v>
+        <v>44593</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19542,11 +19552,11 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>38.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19589,7 +19599,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19603,10 +19613,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45526</v>
+        <v>46265</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19620,11 +19630,11 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19667,7 +19677,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19681,10 +19691,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46155</v>
+        <v>46265</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19702,7 +19712,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19745,7 +19755,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19759,10 +19769,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46155</v>
+        <v>46265</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19780,7 +19790,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19823,7 +19833,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19837,10 +19847,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45929</v>
+        <v>46265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19852,8 +19862,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19896,7 +19911,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19910,10 +19925,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46155</v>
+        <v>45158</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19925,13 +19940,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19974,7 +19984,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 31579-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19988,10 +19998,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46155</v>
+        <v>46224</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20003,13 +20013,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20052,7 +20057,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20066,10 +20071,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46155</v>
+        <v>46224</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20081,13 +20086,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20130,7 +20130,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20144,10 +20144,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46177</v>
+        <v>46268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20203,7 +20203,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20217,10 +20217,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45995</v>
+        <v>45457</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20276,7 +20276,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20290,10 +20290,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46199</v>
+        <v>45457</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20349,7 +20349,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20363,10 +20363,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46211</v>
+        <v>45145</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20422,7 +20422,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20436,10 +20436,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46211</v>
+        <v>44550</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20451,8 +20451,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20495,7 +20500,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20509,10 +20514,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46211</v>
+        <v>46234</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20525,7 +20530,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20568,7 +20573,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20582,10 +20587,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45901</v>
+        <v>46279</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20598,7 +20603,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20641,7 +20646,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20655,10 +20660,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46211</v>
+        <v>46276</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20670,8 +20675,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20714,7 +20724,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 8936-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20728,10 +20738,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46253</v>
+        <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20787,7 +20797,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20801,10 +20811,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20822,7 +20832,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20865,7 +20875,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20879,10 +20889,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46265</v>
+        <v>46239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20900,7 +20910,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20943,7 +20953,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20957,10 +20967,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46265</v>
+        <v>46283</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20978,7 +20988,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21021,7 +21031,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21035,10 +21045,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46265</v>
+        <v>46283</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21056,7 +21066,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21099,7 +21109,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21113,10 +21123,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46265</v>
+        <v>46283</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21134,7 +21144,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21177,7 +21187,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 16281-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21191,10 +21201,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46268</v>
+        <v>45407</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21207,7 +21217,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21250,7 +21260,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21264,10 +21274,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46224</v>
+        <v>46245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21280,7 +21290,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21323,7 +21333,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 31579-2026</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21337,10 +21347,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46224</v>
+        <v>45670</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21353,7 +21363,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21396,7 +21406,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21410,10 +21420,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46276</v>
+        <v>45617</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21425,13 +21435,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21474,7 +21479,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21488,10 +21493,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46279</v>
+        <v>45414</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21504,7 +21509,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21547,7 +21552,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21561,10 +21566,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46234</v>
+        <v>45608</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21577,7 +21582,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21620,7 +21625,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21634,10 +21639,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46281</v>
+        <v>45453</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21649,13 +21654,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21698,7 +21698,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21712,10 +21712,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46239</v>
+        <v>45849</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21793,7 +21793,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44904</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>46089</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45978</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>46111</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45866</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45775</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45229</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45775</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44876</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44560</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44807</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44714</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44491</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44735</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44791</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44834</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45389</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45406</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44879</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44958</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45457</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45414</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44534</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44493</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>46043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45903</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45408</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45231</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44593</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46076</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44957</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45145</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45453</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45364</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44859</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46099</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45191</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45226</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>46099</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45939</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45191</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46107</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44677</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>46107</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46107</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>46113</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>46113</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45317</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45953</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>46113</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>46113</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>46113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>46113</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>46134</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>46134</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46134</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45457</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45457</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>46134</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>46134</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>46134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44791</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45758</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45184</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45147</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45994</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45225</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45091</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45555</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45729</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45070</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>46147</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46147</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46147</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>46147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>46147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45939</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>46154</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46155</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45406</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>46155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>46155</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>46155</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45104</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45370</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45849</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45015</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45352</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44818</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46177</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45461</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45246</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45000</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45191</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45384</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45596</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44550</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46199</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45187</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45158</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46211</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46211</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>46211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45215</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45198</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45714</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>44682</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45166</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45461</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>46265</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46268</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>46224</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44503</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45755</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46276</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45091</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46279</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44896</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46234</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46281</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45208</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46239</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45461</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>46283</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44791</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>46245</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45224</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45147</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45461</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45414</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45638</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45523</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45461</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45191</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44910</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44631</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45714</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45388</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45252</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45636</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45310</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45670</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45617</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45316</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44904</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45953</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46089</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45978</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>46111</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45176</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45866</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>45177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45775</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45229</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45775</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44876</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44560</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44807</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44714</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44491</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44735</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44791</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44834</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>45196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45389</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45406</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44879</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44958</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45457</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>45414</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44534</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44493</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44889</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>46043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45903</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45408</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>45231</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44593</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         <v>46076</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44957</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>45145</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>46021</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>45453</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45364</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44859</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>46099</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45191</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45226</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>46099</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45939</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45191</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46107</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44677</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>46107</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46107</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>46113</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>46113</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45317</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45953</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>46113</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>46113</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>46113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>46113</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>46134</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>46134</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>46134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46134</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45457</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45457</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>46134</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>46134</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>46134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44791</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45758</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45184</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45147</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45994</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45994</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45225</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45091</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44845</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45555</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45729</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45070</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>46147</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46147</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46147</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>46147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>46147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45939</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>46154</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>46155</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>45406</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>46155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>46155</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>46155</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45104</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45370</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45849</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45015</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45352</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44818</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46177</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45461</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45246</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45000</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45191</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45384</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45596</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44550</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46199</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45187</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45158</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46211</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>46211</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>46211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45215</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>46253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45149</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45198</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>45714</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>44682</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45166</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45461</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46265</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46265</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>46265</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46268</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>46224</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>46224</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>44503</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45755</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46276</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45091</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46279</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44896</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46234</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46281</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45208</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46239</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45461</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>46283</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44791</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>46245</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45224</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>44960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45147</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45461</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45414</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>45638</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>44958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45523</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45461</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45191</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44910</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44631</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>45714</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45388</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45252</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45636</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45310</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45670</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45617</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45316</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44904</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45953</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46089</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56956-2025</t>
+          <t>A 33136-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45978</v>
+        <v>45840</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2376,17 +2376,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>22.2</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -2413,12 +2413,131 @@
         <v>6</v>
       </c>
       <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp
+Tallticka
+Smal svampklubba
+Spillkråka
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56956-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
         <v>15</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>15</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tretåig hackspett
@@ -2428,155 +2547,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 33136-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45840</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp
-Tallticka
-Smal svampklubba
-Spillkråka
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
         <v/>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51036-2022</t>
+          <t>A 39837-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44868</v>
+        <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,149 +3453,149 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Stuplav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 51036-2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>44868</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Vårärt
 Blåmossa</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 39837-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45891</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Stuplav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
         <v/>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2261-2026</t>
+          <t>A 16554-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46036</v>
+        <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3852,23 +3852,28 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3880,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -3889,605 +3894,600 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 16642-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45408</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 41696-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 2261-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 2261-2026 artfynd.xlsx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 2261-2026 karta.png", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 2261-2026 georefererad karta.tif", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 2261-2026 FSC-klagomål.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 2261-2026 FSC-klagomål mail.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 2261-2026 tillsynsbegäran.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 2261-2026 tillsynsbegäran mail.docx", "A 2261-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 16554-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 56959-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 16642-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 56959-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56959-2025 artfynd.xlsx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56959-2025 karta.png", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56959-2025 georefererad karta.tif", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56959-2025 FSC-klagomål.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56959-2025 FSC-klagomål mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56959-2025 tillsynsbegäran.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56959-2025 tillsynsbegäran mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56959-2025 prioriterade fågelarter.docx", "A 56959-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 16289-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>46111</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>2.5</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16289-2026 artfynd.xlsx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16289-2026 karta.png", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16289-2026 georefererad karta.tif", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16289-2026 FSC-klagomål.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16289-2026 FSC-klagomål mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16289-2026 tillsynsbegäran.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16289-2026 tillsynsbegäran mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16289-2026 prioriterade fågelarter.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 41696-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
         <v/>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45400</v>
+        <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5188,8 +5188,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5225,46 +5230,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45937</v>
+        <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5294,17 +5299,17 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5318,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5334,42 +5339,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45866</v>
+        <v>45937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5399,13 +5404,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5439,42 +5444,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5488,10 +5493,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45177</v>
+        <v>45741</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5509,22 +5514,22 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5536,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5545,46 +5550,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5594,14 +5599,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45027</v>
+        <v>45741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,8 +5618,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5626,10 +5636,10 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
         <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5654,42 +5664,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5699,14 +5709,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45741</v>
+        <v>45090</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,28 +5728,23 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5751,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5764,42 +5769,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5809,14 +5814,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45741</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5828,13 +5833,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5870,46 +5870,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45177</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -5984,46 +5984,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30586-2026</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6037,10 +6033,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46210</v>
+        <v>45866</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6053,10 +6049,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -6068,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6077,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6093,42 +6089,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 31957-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6138,14 +6134,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45775</v>
+        <v>45510</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,22 +6153,17 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -6187,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -6203,42 +6194,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6252,10 +6243,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45229</v>
+        <v>45219</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,11 +6258,16 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6304,46 +6300,50 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31957-2024</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45510</v>
+        <v>45027</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,20 +6373,20 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
@@ -6397,10 +6397,10 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6413,42 +6413,42 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 30586-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45090</v>
+        <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6487,13 +6487,13 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
         <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6518,35 +6518,35 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
         <v>45775</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44876</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44560</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44807</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44714</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44491</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44530</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44735</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44791</v>
+        <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -8047,7 +8047,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44834</v>
+        <v>44958</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45196</v>
+        <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8149,8 +8149,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8193,7 +8198,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8203,14 +8208,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45389</v>
+        <v>45191</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8223,7 +8228,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8266,7 +8271,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8280,10 +8285,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45406</v>
+        <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8296,7 +8301,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8339,7 +8344,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8349,14 +8354,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44879</v>
+        <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8368,8 +8373,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8412,7 +8422,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8429,7 +8439,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8447,7 +8457,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8490,7 +8500,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8504,10 +8514,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44481</v>
+        <v>45670</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8520,7 +8530,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8563,7 +8573,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8577,10 +8587,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44958</v>
+        <v>45617</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8593,7 +8603,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8636,7 +8646,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8650,10 +8660,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45457</v>
+        <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8666,7 +8676,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8709,7 +8719,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8719,14 +8729,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45414</v>
+        <v>45388</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8739,7 +8749,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8782,7 +8792,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8796,10 +8806,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45279</v>
+        <v>45414</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8811,13 +8821,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8860,7 +8865,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8874,10 +8879,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44534</v>
+        <v>45406</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8890,7 +8895,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8933,7 +8938,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8947,10 +8952,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44493</v>
+        <v>45457</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8963,7 +8968,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9006,7 +9011,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9020,10 +9025,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44862</v>
+        <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9033,11 +9038,6 @@
       <c r="G86" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -9084,7 +9084,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46034</v>
+        <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44889</v>
+        <v>45161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9230,7 +9230,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46043</v>
+        <v>45903</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9303,7 +9303,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9317,10 +9317,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45903</v>
+        <v>45184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9376,7 +9376,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45408</v>
+        <v>45608</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9405,13 +9405,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9454,7 +9449,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9468,10 +9463,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45231</v>
+        <v>45147</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9484,7 +9479,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9527,7 +9522,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9537,14 +9532,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44593</v>
+        <v>45166</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9556,13 +9551,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>38.4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9605,7 +9595,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9619,10 +9609,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46076</v>
+        <v>45453</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9634,13 +9624,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9683,7 +9668,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9697,10 +9682,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44957</v>
+        <v>45638</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9713,7 +9698,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9756,7 +9741,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9770,10 +9755,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45145</v>
+        <v>45258</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9786,7 +9771,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9829,7 +9814,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9843,10 +9828,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46021</v>
+        <v>45091</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9858,8 +9843,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9902,7 +9892,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9916,10 +9906,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45608</v>
+        <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9932,7 +9922,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9975,7 +9965,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9989,10 +9979,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44593</v>
+        <v>44818</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10004,8 +9994,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10048,7 +10043,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10062,10 +10057,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45453</v>
+        <v>45461</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10078,7 +10073,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.6</v>
+        <v>12.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10121,7 +10116,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10131,14 +10126,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45364</v>
+        <v>45406</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10150,13 +10145,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10216,7 +10206,7 @@
         <v>45825</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10272,7 +10262,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10282,14 +10272,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44859</v>
+        <v>45939</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10302,7 +10292,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10345,7 +10335,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10359,10 +10349,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46099</v>
+        <v>45849</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10374,8 +10364,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10418,7 +10413,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10432,10 +10427,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45191</v>
+        <v>45947</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10448,7 +10443,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10491,7 +10486,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10505,10 +10500,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45226</v>
+        <v>44481</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10521,7 +10516,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10564,7 +10559,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10578,10 +10573,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46099</v>
+        <v>44896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10593,8 +10588,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10637,7 +10637,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45939</v>
+        <v>45187</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10666,8 +10666,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10710,7 +10715,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10724,10 +10729,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45947</v>
+        <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10740,7 +10745,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10783,7 +10788,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10793,14 +10798,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45191</v>
+        <v>45953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10812,8 +10817,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10856,7 +10866,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10870,10 +10880,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46107</v>
+        <v>45279</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10885,8 +10895,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10929,7 +10944,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10943,10 +10958,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44677</v>
+        <v>45596</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10956,6 +10971,11 @@
       <c r="G112" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -11002,7 +11022,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11016,10 +11036,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46107</v>
+        <v>46034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11032,7 +11052,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11075,7 +11095,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11089,10 +11109,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46107</v>
+        <v>45965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11148,7 +11168,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11162,10 +11182,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46113</v>
+        <v>44593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11177,13 +11197,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11226,7 +11241,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11240,10 +11255,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46113</v>
+        <v>45636</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11255,13 +11270,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11304,7 +11314,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11318,10 +11328,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46113</v>
+        <v>45714</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11333,13 +11343,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11382,7 +11387,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11396,10 +11401,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45317</v>
+        <v>44957</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11412,7 +11417,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11455,7 +11460,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11465,14 +11470,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45953</v>
+        <v>46043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11484,13 +11489,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11533,7 +11533,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46113</v>
+        <v>45198</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11562,13 +11562,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11611,7 +11606,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11625,10 +11620,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46113</v>
+        <v>45985</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11640,13 +11635,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11689,7 +11679,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11703,10 +11693,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46113</v>
+        <v>45384</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11718,13 +11708,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11767,7 +11752,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11781,10 +11766,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45714</v>
+        <v>45461</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11797,7 +11782,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11840,7 +11825,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11854,10 +11839,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46113</v>
+        <v>45994</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11869,13 +11854,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11918,7 +11898,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11932,10 +11912,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45965</v>
+        <v>45994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11948,7 +11928,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11991,7 +11971,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12005,10 +11985,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46134</v>
+        <v>44960</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12022,11 +12002,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12069,7 +12049,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12083,10 +12063,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46134</v>
+        <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12098,13 +12078,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12147,7 +12122,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12161,10 +12136,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46134</v>
+        <v>45252</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12174,11 +12149,6 @@
       <c r="G128" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -12225,7 +12195,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12239,10 +12209,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46134</v>
+        <v>45317</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12254,13 +12224,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12303,7 +12268,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12317,10 +12282,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46134</v>
+        <v>45196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12332,13 +12297,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12381,7 +12341,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12395,10 +12355,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46134</v>
+        <v>45149</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12410,13 +12370,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12459,7 +12414,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12473,10 +12428,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45457</v>
+        <v>44834</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12489,7 +12444,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12532,7 +12487,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12546,10 +12501,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45457</v>
+        <v>46076</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12561,8 +12516,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12605,7 +12565,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12619,10 +12579,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46134</v>
+        <v>46021</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12634,13 +12594,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12683,7 +12638,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12697,10 +12652,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12712,13 +12667,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12761,7 +12711,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12775,10 +12725,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12790,13 +12740,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12839,7 +12784,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12853,10 +12798,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45740</v>
+        <v>45279</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12868,8 +12813,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12912,7 +12862,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12926,10 +12876,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45985</v>
+        <v>45191</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12942,7 +12892,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12985,7 +12935,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12995,14 +12945,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44791</v>
+        <v>45364</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13020,7 +12970,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13063,7 +13013,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13077,10 +13027,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45758</v>
+        <v>46107</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13093,7 +13043,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13136,7 +13086,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13150,10 +13100,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45184</v>
+        <v>46107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13166,7 +13116,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13209,7 +13159,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13223,10 +13173,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45147</v>
+        <v>46107</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13239,7 +13189,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13282,7 +13232,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13296,10 +13246,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45994</v>
+        <v>45215</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13312,7 +13262,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13355,7 +13305,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13369,10 +13319,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45994</v>
+        <v>46113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13384,8 +13334,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13428,7 +13383,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13442,10 +13397,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45225</v>
+        <v>46113</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13457,8 +13412,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13501,7 +13461,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13515,10 +13475,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45091</v>
+        <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13532,11 +13492,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13579,7 +13539,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13593,10 +13553,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45161</v>
+        <v>45246</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13608,8 +13568,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13652,7 +13617,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13666,10 +13631,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44845</v>
+        <v>46113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13681,8 +13646,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13725,7 +13695,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13739,10 +13709,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45555</v>
+        <v>45755</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13755,7 +13725,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13798,7 +13768,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13812,10 +13782,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45729</v>
+        <v>46113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13827,8 +13797,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13871,7 +13846,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13881,14 +13856,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45532</v>
+        <v>46113</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13900,8 +13875,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13944,7 +13924,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13958,10 +13938,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45070</v>
+        <v>46113</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13973,8 +13953,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14017,7 +14002,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14031,10 +14016,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46147</v>
+        <v>45105</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14046,13 +14031,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14095,7 +14075,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14109,10 +14089,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46147</v>
+        <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14124,13 +14104,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14173,7 +14148,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14187,10 +14162,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46147</v>
+        <v>44791</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14208,7 +14183,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14251,7 +14226,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14265,10 +14240,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46147</v>
+        <v>45161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14280,13 +14255,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14329,7 +14299,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21276-2026</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14343,10 +14313,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46147</v>
+        <v>45000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14364,7 +14334,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14407,7 +14377,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14417,14 +14387,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45939</v>
+        <v>46134</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14436,8 +14406,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14480,7 +14455,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14494,10 +14469,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46154</v>
+        <v>46134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14515,7 +14490,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14558,7 +14533,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 19510-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14572,10 +14547,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46155</v>
+        <v>46134</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14636,7 +14611,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 19512-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14650,10 +14625,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45406</v>
+        <v>46134</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14663,6 +14638,11 @@
       <c r="G161" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -14709,7 +14689,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14723,10 +14703,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45526</v>
+        <v>46134</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14740,11 +14720,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14787,7 +14767,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14801,10 +14781,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46155</v>
+        <v>46134</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14822,7 +14802,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14865,7 +14845,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14879,10 +14859,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46155</v>
+        <v>46134</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14900,7 +14880,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14943,7 +14923,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14957,10 +14937,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45929</v>
+        <v>46134</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14972,8 +14952,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15016,7 +15001,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15030,10 +15015,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46155</v>
+        <v>46134</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15051,7 +15036,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15094,7 +15079,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15108,10 +15093,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46155</v>
+        <v>45740</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15121,11 +15106,6 @@
       <c r="G167" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -15172,7 +15152,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15186,10 +15166,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46155</v>
+        <v>45310</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15201,13 +15181,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15250,7 +15225,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15264,10 +15239,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45104</v>
+        <v>44845</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15280,7 +15255,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15323,7 +15298,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15337,10 +15312,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45258</v>
+        <v>45555</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15353,7 +15328,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15396,7 +15371,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15410,10 +15385,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45161</v>
+        <v>45098</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15426,7 +15401,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15469,7 +15444,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15479,14 +15454,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45370</v>
+        <v>45532</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15498,13 +15473,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15547,7 +15517,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15561,10 +15531,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45849</v>
+        <v>45729</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15576,13 +15546,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15625,7 +15590,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15635,14 +15600,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45015</v>
+        <v>45389</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15655,7 +15620,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15698,7 +15663,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15712,10 +15677,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45352</v>
+        <v>44958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15728,7 +15693,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15771,7 +15736,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15785,10 +15750,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44818</v>
+        <v>45461</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15800,13 +15765,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15849,7 +15809,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15859,14 +15819,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46177</v>
+        <v>44879</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15879,7 +15839,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15922,7 +15882,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15936,10 +15896,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45461</v>
+        <v>45224</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15952,7 +15912,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15995,7 +15955,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16009,10 +15969,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45246</v>
+        <v>45414</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16024,13 +15984,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16073,7 +16028,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16087,10 +16042,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45000</v>
+        <v>46147</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16151,7 +16106,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16165,10 +16120,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45191</v>
+        <v>46147</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16180,8 +16135,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16224,7 +16184,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 21276-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16238,10 +16198,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45384</v>
+        <v>46147</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16253,8 +16213,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16297,7 +16262,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16311,10 +16276,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45596</v>
+        <v>46147</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16332,7 +16297,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16375,7 +16340,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16389,10 +16354,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45995</v>
+        <v>46147</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16404,8 +16369,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16448,7 +16418,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16462,10 +16432,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44550</v>
+        <v>45408</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16483,7 +16453,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16526,7 +16496,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16540,10 +16510,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45555</v>
+        <v>44682</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16556,7 +16526,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16599,7 +16569,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16613,10 +16583,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46199</v>
+        <v>45929</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16629,7 +16599,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16672,7 +16642,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16686,10 +16656,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45187</v>
+        <v>45939</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16701,13 +16671,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16750,7 +16715,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16764,10 +16729,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45158</v>
+        <v>46155</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16779,8 +16744,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16823,7 +16793,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16837,10 +16807,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46211</v>
+        <v>46155</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16852,8 +16822,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16896,7 +16871,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16910,10 +16885,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46211</v>
+        <v>46155</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16925,8 +16900,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16969,7 +16949,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16983,10 +16963,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46211</v>
+        <v>44859</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16999,7 +16979,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17042,7 +17022,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17056,10 +17036,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45901</v>
+        <v>46155</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17071,8 +17051,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17115,7 +17100,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17129,10 +17114,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46211</v>
+        <v>45526</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17144,8 +17129,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17188,7 +17178,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17202,10 +17192,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45215</v>
+        <v>46154</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17217,8 +17207,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17261,7 +17256,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17275,10 +17270,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46253</v>
+        <v>46155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17290,8 +17285,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17348,10 +17348,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45149</v>
+        <v>46155</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17363,8 +17363,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17407,7 +17412,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17421,10 +17426,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45198</v>
+        <v>44889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17437,7 +17442,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17480,7 +17485,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17494,10 +17499,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45714</v>
+        <v>45091</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17509,8 +17514,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17553,7 +17563,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17567,10 +17577,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44682</v>
+        <v>45015</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17583,7 +17593,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17626,7 +17636,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17640,10 +17650,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45166</v>
+        <v>45191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17656,7 +17666,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17699,7 +17709,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17713,10 +17723,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45461</v>
+        <v>44910</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17729,7 +17739,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17772,7 +17782,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17786,10 +17796,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46265</v>
+        <v>45758</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17801,13 +17811,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17850,7 +17855,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17864,10 +17869,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46265</v>
+        <v>45555</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17879,13 +17884,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17928,7 +17928,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17942,10 +17942,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46265</v>
+        <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17957,13 +17957,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18006,7 +18001,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18020,10 +18015,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46265</v>
+        <v>44618</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18035,13 +18030,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18084,7 +18074,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18098,10 +18088,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46265</v>
+        <v>45523</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18113,13 +18103,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18162,7 +18147,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18176,10 +18161,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45267</v>
+        <v>45147</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18192,7 +18177,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18235,7 +18220,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18249,10 +18234,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46268</v>
+        <v>44677</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18265,7 +18250,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18308,7 +18293,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18322,10 +18307,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46224</v>
+        <v>44791</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18338,7 +18323,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18381,7 +18366,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31579-2026</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18395,10 +18380,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46224</v>
+        <v>45225</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18411,7 +18396,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18454,7 +18439,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18468,10 +18453,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44503</v>
+        <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18484,7 +18469,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18527,7 +18512,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18541,10 +18526,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45755</v>
+        <v>45995</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18557,7 +18542,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18600,7 +18585,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18614,10 +18599,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46276</v>
+        <v>46199</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18629,13 +18614,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18678,7 +18658,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18692,10 +18672,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45091</v>
+        <v>45267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18707,13 +18687,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18756,7 +18731,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18770,10 +18745,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46279</v>
+        <v>44493</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18786,7 +18761,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18829,7 +18804,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18843,10 +18818,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44896</v>
+        <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18864,7 +18839,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18907,7 +18882,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18921,10 +18896,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46234</v>
+        <v>45352</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18937,7 +18912,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18980,7 +18955,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18994,10 +18969,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46281</v>
+        <v>45461</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19009,13 +18984,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19058,7 +19028,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19072,10 +19042,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45208</v>
+        <v>46253</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19088,7 +19058,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19131,7 +19101,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19145,10 +19115,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46239</v>
+        <v>44534</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19160,13 +19130,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19209,7 +19174,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19223,10 +19188,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45461</v>
+        <v>45070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19239,7 +19204,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19282,7 +19247,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19296,10 +19261,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46283</v>
+        <v>46211</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19311,13 +19276,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19360,7 +19320,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19374,10 +19334,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46283</v>
+        <v>46211</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19389,13 +19349,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19438,7 +19393,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19452,10 +19407,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44791</v>
+        <v>46211</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19467,13 +19422,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19516,7 +19466,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19530,10 +19480,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46283</v>
+        <v>45901</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19545,13 +19495,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19594,7 +19539,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19608,10 +19553,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46245</v>
+        <v>46211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19624,7 +19569,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19667,7 +19612,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19681,10 +19626,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45224</v>
+        <v>44631</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19696,8 +19641,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19740,7 +19690,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19750,14 +19700,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44960</v>
+        <v>44593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19771,11 +19721,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.2</v>
+        <v>38.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19818,7 +19768,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19832,10 +19782,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45147</v>
+        <v>46265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19847,8 +19797,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19891,7 +19846,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19905,10 +19860,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45461</v>
+        <v>46265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19920,8 +19875,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19964,7 +19924,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19978,10 +19938,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45266</v>
+        <v>45158</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19994,7 +19954,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20037,7 +19997,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20051,10 +20011,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45414</v>
+        <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20066,8 +20026,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20110,7 +20075,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20124,10 +20089,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45638</v>
+        <v>46265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20139,8 +20104,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20183,7 +20153,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20197,10 +20167,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44958</v>
+        <v>46265</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20212,8 +20182,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20256,7 +20231,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 31579-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20270,10 +20245,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45523</v>
+        <v>46224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20286,7 +20261,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20329,7 +20304,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20343,10 +20318,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45105</v>
+        <v>45457</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20359,7 +20334,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20402,7 +20377,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20416,10 +20391,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45461</v>
+        <v>45457</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20432,7 +20407,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20475,7 +20450,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20489,10 +20464,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45182</v>
+        <v>46224</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20505,7 +20480,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20548,7 +20523,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20562,10 +20537,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45191</v>
+        <v>46268</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20578,7 +20553,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20621,7 +20596,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20635,10 +20610,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44910</v>
+        <v>45145</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20651,7 +20626,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20694,7 +20669,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20708,10 +20683,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44631</v>
+        <v>44550</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20789,7 +20764,7 @@
         <v>45714</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20845,7 +20820,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20859,10 +20834,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45098</v>
+        <v>46234</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20875,7 +20850,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20918,7 +20893,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20928,14 +20903,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45388</v>
+        <v>46279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20948,7 +20923,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20991,7 +20966,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21005,10 +20980,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45279</v>
+        <v>46276</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21026,7 +21001,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21069,7 +21044,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21083,10 +21058,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45252</v>
+        <v>46281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21098,8 +21073,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21142,7 +21122,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21156,10 +21136,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45636</v>
+        <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21171,8 +21151,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21215,7 +21200,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21229,10 +21214,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44618</v>
+        <v>46283</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21244,8 +21229,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21288,7 +21278,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21302,10 +21292,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45310</v>
+        <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21317,8 +21307,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21361,7 +21356,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 16281-2024</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21375,10 +21370,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45407</v>
+        <v>46283</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21390,8 +21385,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21434,7 +21434,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 16281-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21448,10 +21448,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45670</v>
+        <v>45407</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21507,7 +21507,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21521,10 +21521,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45617</v>
+        <v>46245</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21597,7 +21597,7 @@
         <v>45316</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44904</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45953</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46089</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51036-2022</t>
+          <t>A 39837-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44868</v>
+        <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,149 +3453,149 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Stuplav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 51036-2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>44868</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Vårärt
 Blåmossa</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 39837-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45891</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Stuplav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
         <v/>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2261-2026</t>
+          <t>A 16554-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46036</v>
+        <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3852,23 +3852,28 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3880,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -3889,277 +3894,272 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 16642-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45408</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Bivråk
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 2261-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 2261-2026 artfynd.xlsx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 2261-2026 karta.png", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 2261-2026 georefererad karta.tif", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 2261-2026 FSC-klagomål.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 2261-2026 FSC-klagomål mail.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 2261-2026 tillsynsbegäran.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 2261-2026 tillsynsbegäran mail.docx", "A 2261-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 16554-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16554-2024 artfynd.xlsx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16554-2024 karta.png", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16554-2024 georefererad karta.tif", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16554-2024 FSC-klagomål.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16554-2024 FSC-klagomål mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16554-2024 tillsynsbegäran.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16554-2024 tillsynsbegäran mail.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16554-2024 prioriterade fågelarter.docx", "A 16554-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 16642-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45408</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Bivråk
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16642-2024 artfynd.xlsx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16642-2024 karta.png", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16642-2024 georefererad karta.tif", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16642-2024 FSC-klagomål.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16642-2024 FSC-klagomål mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16642-2024 tillsynsbegäran.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16642-2024 tillsynsbegäran mail.docx", "A 16642-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16642-2024 prioriterade fågelarter.docx", "A 16642-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56959-2025</t>
+          <t>A 41696-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45978</v>
+        <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4188,22 +4188,17 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4218,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4227,267 +4222,272 @@
         <v>2</v>
       </c>
       <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 56959-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56959-2025 artfynd.xlsx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56959-2025 karta.png", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56959-2025 georefererad karta.tif", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56959-2025 FSC-klagomål.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56959-2025 FSC-klagomål mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56959-2025 tillsynsbegäran.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56959-2025 tillsynsbegäran mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56959-2025 prioriterade fågelarter.docx", "A 56959-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 16289-2026</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>46111</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>2.5</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16289-2026 artfynd.xlsx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16289-2026 karta.png", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16289-2026 georefererad karta.tif", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16289-2026 FSC-klagomål.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16289-2026 FSC-klagomål mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16289-2026 tillsynsbegäran.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16289-2026 tillsynsbegäran mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16289-2026 prioriterade fågelarter.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 41696-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
         <v/>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45400</v>
+        <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5188,8 +5188,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5225,46 +5230,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45937</v>
+        <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5294,17 +5299,17 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5318,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5334,42 +5339,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5379,14 +5384,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45741</v>
+        <v>45937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,20 +5403,15 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5444,42 +5444,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5489,14 +5489,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45741</v>
+        <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,13 +5508,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5523,13 +5518,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5541,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5550,46 +5545,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5603,10 +5598,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45866</v>
+        <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,17 +5614,17 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
@@ -5643,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5659,42 +5654,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5704,14 +5699,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45177</v>
+        <v>45866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5723,22 +5718,17 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5753,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5765,46 +5755,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5814,14 +5804,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45027</v>
+        <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,11 +5823,16 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5846,10 +5841,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
         <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5870,46 +5865,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5919,14 +5914,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45219</v>
+        <v>45741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5940,26 +5935,26 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5971,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5984,46 +5979,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30586-2026</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6033,14 +6024,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46210</v>
+        <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,8 +6043,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6062,13 +6058,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6080,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6089,46 +6085,46 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 30586-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6138,14 +6134,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45775</v>
+        <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6157,13 +6153,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6172,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
         <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6190,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6199,46 +6190,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 31957-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6252,10 +6243,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45229</v>
+        <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,16 +6259,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6292,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6304,46 +6295,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 31957-2024</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6357,10 +6348,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45510</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,8 +6363,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6382,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -6397,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -6413,42 +6409,46 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40337-2026</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46294</v>
+        <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,13 +6477,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6492,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6510,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6519,46 +6514,46 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 40337-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6572,10 +6567,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45090</v>
+        <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6587,8 +6582,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6628,35 +6628,35 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44791</v>
+        <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45196</v>
+        <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44834</v>
+        <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8259,8 +8259,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8303,7 +8308,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8317,10 +8322,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45406</v>
+        <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8333,7 +8338,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8376,7 +8381,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8386,14 +8391,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45389</v>
+        <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8406,7 +8411,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8449,7 +8454,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8466,7 +8471,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8484,7 +8489,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8527,7 +8532,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8537,14 +8542,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44879</v>
+        <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8557,7 +8562,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8600,7 +8605,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8614,10 +8619,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44481</v>
+        <v>44862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8629,8 +8634,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8673,7 +8683,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8687,10 +8697,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44958</v>
+        <v>45670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8703,7 +8713,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8746,7 +8756,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8756,14 +8766,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45670</v>
+        <v>45388</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8776,7 +8786,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8819,7 +8829,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8833,10 +8843,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45617</v>
+        <v>45406</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8849,7 +8859,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8892,7 +8902,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8906,10 +8916,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45457</v>
+        <v>45617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8922,7 +8932,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8965,7 +8975,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8979,10 +8989,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45414</v>
+        <v>45457</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8995,7 +9005,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9038,7 +9048,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9052,10 +9062,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46034</v>
+        <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9068,7 +9078,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9111,7 +9121,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9125,10 +9135,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44862</v>
+        <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9140,13 +9150,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9189,7 +9194,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9203,10 +9208,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45279</v>
+        <v>45161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9218,13 +9223,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9267,7 +9267,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46043</v>
+        <v>45184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9340,7 +9340,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9354,10 +9354,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44534</v>
+        <v>45147</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44493</v>
+        <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9486,7 +9486,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9500,10 +9500,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44889</v>
+        <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9559,7 +9559,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9573,10 +9573,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45903</v>
+        <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46076</v>
+        <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9661,13 +9661,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9710,7 +9705,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9724,10 +9719,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45408</v>
+        <v>45258</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9739,13 +9734,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9788,7 +9778,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9802,10 +9792,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46021</v>
+        <v>46043</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9861,7 +9851,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9875,10 +9865,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45231</v>
+        <v>45414</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9891,7 +9881,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9934,7 +9924,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9944,14 +9934,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44593</v>
+        <v>45091</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9965,11 +9955,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>38.4</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10012,7 +10002,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29669-2025</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10026,10 +10016,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45825</v>
+        <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10042,7 +10032,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10085,7 +10075,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10099,10 +10089,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44957</v>
+        <v>45608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10115,7 +10105,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10158,7 +10148,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10172,10 +10162,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45145</v>
+        <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10187,8 +10177,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10231,7 +10226,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10245,10 +10240,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45608</v>
+        <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10261,7 +10256,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.3</v>
+        <v>12.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10304,7 +10299,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10314,14 +10309,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45939</v>
+        <v>45406</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10334,7 +10329,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10377,7 +10372,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10391,10 +10386,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44593</v>
+        <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10407,7 +10402,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10450,7 +10445,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10464,10 +10459,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45947</v>
+        <v>44481</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10480,7 +10475,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10523,7 +10518,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10537,10 +10532,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45453</v>
+        <v>44896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10552,8 +10547,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10596,7 +10596,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10606,14 +10606,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46099</v>
+        <v>45187</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10625,8 +10625,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10669,7 +10674,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 29669-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10683,10 +10688,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46099</v>
+        <v>45825</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10699,7 +10704,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10742,7 +10747,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10752,14 +10757,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45364</v>
+        <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10771,13 +10776,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10830,14 +10830,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45953</v>
+        <v>46076</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10851,11 +10851,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10898,7 +10898,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10908,14 +10908,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44859</v>
+        <v>45939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10971,7 +10971,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45191</v>
+        <v>45947</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11058,10 +11058,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45226</v>
+        <v>45279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11073,8 +11073,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11117,7 +11122,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11131,10 +11136,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46107</v>
+        <v>46021</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11147,7 +11152,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11190,7 +11195,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11200,14 +11205,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46107</v>
+        <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11219,8 +11224,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11263,7 +11273,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11277,10 +11287,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46107</v>
+        <v>44593</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11293,7 +11303,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11336,7 +11346,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11350,10 +11360,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45191</v>
+        <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11366,7 +11376,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11409,7 +11419,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11423,10 +11433,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45965</v>
+        <v>45714</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11439,7 +11449,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11482,7 +11492,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11496,10 +11506,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46113</v>
+        <v>44957</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11511,13 +11521,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11560,7 +11565,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11574,10 +11579,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46113</v>
+        <v>45965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11589,13 +11594,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11638,7 +11638,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11652,10 +11652,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11667,13 +11667,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11716,7 +11711,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11730,10 +11725,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46113</v>
+        <v>45198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11745,13 +11740,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11794,7 +11784,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11808,10 +11798,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11823,13 +11813,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11872,7 +11857,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11886,10 +11871,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44677</v>
+        <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11902,7 +11887,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11945,7 +11930,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11959,10 +11944,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11974,13 +11959,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12023,7 +12003,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12037,10 +12017,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46113</v>
+        <v>45461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12052,13 +12032,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12101,7 +12076,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12115,10 +12090,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45317</v>
+        <v>46107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12131,7 +12106,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12174,7 +12149,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12188,10 +12163,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45714</v>
+        <v>46107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12204,7 +12179,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12247,7 +12222,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12261,10 +12236,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46134</v>
+        <v>45985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12276,13 +12251,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12325,7 +12295,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12339,10 +12309,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12360,7 +12330,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12403,7 +12373,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12417,10 +12387,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12438,7 +12408,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12481,7 +12451,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12495,10 +12465,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12516,7 +12486,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12559,7 +12529,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12573,10 +12543,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12594,7 +12564,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12637,7 +12607,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12651,10 +12621,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46134</v>
+        <v>44960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12668,11 +12638,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12715,7 +12685,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12729,10 +12699,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12750,7 +12720,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12793,7 +12763,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12807,10 +12777,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12828,7 +12798,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12871,7 +12841,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12885,10 +12855,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45985</v>
+        <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12900,8 +12870,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12944,7 +12919,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12958,10 +12933,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46134</v>
+        <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12973,13 +12948,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13022,7 +12992,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13036,10 +13006,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45457</v>
+        <v>45191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13052,7 +13022,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13095,7 +13065,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13109,10 +13079,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45457</v>
+        <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13125,7 +13095,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13168,7 +13138,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13182,10 +13152,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45740</v>
+        <v>45252</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13198,7 +13168,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13241,7 +13211,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13255,10 +13225,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45994</v>
+        <v>46134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13270,8 +13240,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>9.4</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13314,7 +13289,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13328,10 +13303,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45994</v>
+        <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13343,8 +13318,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13387,7 +13367,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 19510-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13401,10 +13381,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44791</v>
+        <v>46134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13422,7 +13402,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13465,7 +13445,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 19512-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13479,10 +13459,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45758</v>
+        <v>46134</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13494,8 +13474,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13538,7 +13523,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13552,10 +13537,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45184</v>
+        <v>46134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13567,8 +13552,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13611,7 +13601,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13625,10 +13615,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45147</v>
+        <v>46134</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13640,8 +13630,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13684,7 +13679,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13698,10 +13693,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45225</v>
+        <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13713,8 +13708,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13771,10 +13771,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45091</v>
+        <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13788,11 +13788,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13835,7 +13835,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45161</v>
+        <v>45317</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13908,7 +13908,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44845</v>
+        <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45849</v>
+        <v>45149</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14010,13 +14010,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14059,7 +14054,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14073,10 +14068,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45555</v>
+        <v>46134</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14088,8 +14083,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14132,7 +14132,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14146,10 +14146,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45729</v>
+        <v>44834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14205,7 +14205,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45596</v>
+        <v>45849</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14283,7 +14283,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14293,14 +14293,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45070</v>
+        <v>45532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14356,7 +14356,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14366,14 +14366,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45532</v>
+        <v>45729</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14443,10 +14443,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46147</v>
+        <v>45279</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14507,7 +14507,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46147</v>
+        <v>45191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14536,13 +14536,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14585,7 +14580,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14595,14 +14590,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46147</v>
+        <v>45364</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14620,7 +14615,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14663,7 +14658,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14677,10 +14672,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46147</v>
+        <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14692,13 +14687,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14741,7 +14731,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21276-2026</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14755,10 +14745,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46147</v>
+        <v>45246</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14776,7 +14766,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14819,7 +14809,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14833,10 +14823,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45406</v>
+        <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14849,7 +14839,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14892,7 +14882,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14902,14 +14892,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45939</v>
+        <v>45105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14922,7 +14912,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14965,7 +14955,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14979,10 +14969,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46154</v>
+        <v>45208</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14994,13 +14984,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15043,7 +15028,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15057,10 +15042,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46155</v>
+        <v>44791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15078,7 +15063,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15121,7 +15106,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15135,10 +15120,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45104</v>
+        <v>45161</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15151,7 +15136,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15194,7 +15179,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15208,10 +15193,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45258</v>
+        <v>45596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15223,8 +15208,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15267,7 +15257,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15281,10 +15271,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45526</v>
+        <v>46147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15298,11 +15288,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15345,7 +15335,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15359,10 +15349,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46155</v>
+        <v>45000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15380,7 +15370,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15423,7 +15413,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15437,10 +15427,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15448,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15501,7 +15491,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 21276-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15515,10 +15505,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45929</v>
+        <v>46147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15530,8 +15520,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15574,7 +15569,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15588,10 +15583,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15609,7 +15604,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15652,7 +15647,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15666,10 +15661,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15687,7 +15682,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15730,7 +15725,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15744,10 +15739,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46155</v>
+        <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15759,13 +15754,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15808,7 +15798,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15822,10 +15812,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45161</v>
+        <v>45929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15838,7 +15828,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15881,7 +15871,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15891,14 +15881,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45370</v>
+        <v>45939</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15910,13 +15900,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15959,7 +15944,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15973,10 +15958,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45015</v>
+        <v>46155</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15988,8 +15973,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16032,7 +16022,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16046,10 +16036,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45352</v>
+        <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16061,8 +16051,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16105,7 +16100,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16119,10 +16114,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44818</v>
+        <v>46155</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16140,7 +16135,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16183,7 +16178,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16197,10 +16192,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45461</v>
+        <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16212,8 +16207,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16256,7 +16256,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16270,10 +16270,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45246</v>
+        <v>45526</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16287,11 +16287,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16334,7 +16334,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45000</v>
+        <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16426,10 +16426,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45191</v>
+        <v>45310</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16485,7 +16485,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16499,10 +16499,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46177</v>
+        <v>44845</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16558,7 +16558,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16572,10 +16572,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45384</v>
+        <v>46155</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16587,8 +16587,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16631,7 +16636,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16645,10 +16650,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44550</v>
+        <v>46155</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16666,7 +16671,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16709,7 +16714,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16726,7 +16731,7 @@
         <v>45555</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16739,7 +16744,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16782,7 +16787,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16792,14 +16797,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45187</v>
+        <v>45098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16811,13 +16816,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16870,14 +16870,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45158</v>
+        <v>45389</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16933,7 +16933,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45995</v>
+        <v>44958</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17020,10 +17020,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45215</v>
+        <v>45461</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17089,14 +17089,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46199</v>
+        <v>44879</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17152,7 +17152,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45149</v>
+        <v>46177</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17225,7 +17225,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45198</v>
+        <v>45224</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17298,7 +17298,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17312,10 +17312,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45714</v>
+        <v>45414</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17371,7 +17371,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44682</v>
+        <v>45408</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17400,8 +17400,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17444,7 +17449,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17458,10 +17463,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46211</v>
+        <v>44682</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17474,7 +17479,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17517,7 +17522,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17531,10 +17536,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46211</v>
+        <v>44859</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17547,7 +17552,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17590,7 +17595,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17604,10 +17609,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46211</v>
+        <v>45995</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17620,7 +17625,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17663,7 +17668,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17677,10 +17682,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45901</v>
+        <v>46199</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17693,7 +17698,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17736,7 +17741,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17750,10 +17755,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46211</v>
+        <v>44889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17766,7 +17771,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17809,7 +17814,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17823,10 +17828,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45166</v>
+        <v>45091</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17838,8 +17843,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17882,7 +17892,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17896,10 +17906,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45461</v>
+        <v>45015</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17912,7 +17922,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17955,7 +17965,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17969,10 +17979,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45267</v>
+        <v>45191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17985,7 +17995,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18028,7 +18038,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18042,10 +18052,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44503</v>
+        <v>46211</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18058,7 +18068,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18101,7 +18111,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18115,10 +18125,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46265</v>
+        <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18130,13 +18140,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18179,7 +18184,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18193,10 +18198,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46265</v>
+        <v>46211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18208,13 +18213,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46265</v>
+        <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18286,13 +18286,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18335,7 +18330,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18349,10 +18344,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46265</v>
+        <v>46211</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18364,13 +18359,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18413,7 +18403,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18427,10 +18417,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46265</v>
+        <v>44910</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18442,13 +18432,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18491,7 +18476,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18505,10 +18490,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46268</v>
+        <v>45758</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18521,7 +18506,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18564,7 +18549,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18578,10 +18563,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18593,8 +18578,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18637,7 +18627,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18651,10 +18641,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45755</v>
+        <v>45555</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18667,7 +18657,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18710,7 +18700,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31579-2026</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18724,10 +18714,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18739,8 +18729,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18783,7 +18778,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18797,10 +18792,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45091</v>
+        <v>46265</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18814,11 +18809,11 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18861,7 +18856,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18875,10 +18870,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44896</v>
+        <v>46265</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18896,7 +18891,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18939,7 +18934,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18953,10 +18948,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45208</v>
+        <v>46265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18968,8 +18963,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19012,7 +19012,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 31579-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19026,10 +19026,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45461</v>
+        <v>46224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19085,7 +19085,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19099,10 +19099,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44791</v>
+        <v>46224</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19114,13 +19114,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19163,7 +19158,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19177,10 +19172,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19192,13 +19187,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19241,7 +19231,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19255,10 +19245,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46279</v>
+        <v>44618</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19271,7 +19261,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19314,7 +19304,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19328,10 +19318,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46234</v>
+        <v>45523</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19344,7 +19334,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19387,7 +19377,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19401,10 +19391,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46281</v>
+        <v>45147</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19416,13 +19406,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19465,7 +19450,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19479,10 +19464,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19494,13 +19479,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19543,7 +19523,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19557,10 +19537,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45224</v>
+        <v>46279</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19573,7 +19553,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19616,7 +19596,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19630,10 +19610,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19651,7 +19631,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19694,7 +19674,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19708,10 +19688,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44960</v>
+        <v>44677</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19723,13 +19703,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19772,7 +19747,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19786,10 +19761,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45147</v>
+        <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19801,8 +19776,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19845,7 +19825,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19859,10 +19839,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46283</v>
+        <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19880,7 +19860,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19923,7 +19903,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19937,10 +19917,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46283</v>
+        <v>44791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19952,13 +19932,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20001,7 +19976,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20015,10 +19990,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46245</v>
+        <v>46283</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20030,8 +20005,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20074,7 +20054,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20088,10 +20068,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45461</v>
+        <v>46283</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20103,8 +20083,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>12.2</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20147,7 +20132,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20161,10 +20146,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45266</v>
+        <v>46283</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20176,8 +20161,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20220,7 +20210,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20234,10 +20224,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45414</v>
+        <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20250,7 +20240,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20293,7 +20283,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20307,10 +20297,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45638</v>
+        <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20323,7 +20313,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20366,7 +20356,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20380,10 +20370,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44958</v>
+        <v>45267</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20396,7 +20386,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20439,7 +20429,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20453,10 +20443,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45523</v>
+        <v>44493</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20512,7 +20502,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 40336-2026</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20526,10 +20516,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46294</v>
+        <v>45370</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20547,7 +20537,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20590,7 +20580,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 40335-2026</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20604,10 +20594,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46294</v>
+        <v>45352</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20619,13 +20609,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20668,7 +20653,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20682,10 +20667,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45105</v>
+        <v>45461</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20698,7 +20683,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20741,7 +20726,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20755,10 +20740,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45461</v>
+        <v>44534</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20771,7 +20756,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20814,7 +20799,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20828,10 +20813,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45182</v>
+        <v>45070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20844,7 +20829,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20887,7 +20872,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 40527-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20901,10 +20886,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45191</v>
+        <v>46295</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20916,8 +20901,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20960,7 +20950,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 40570-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20974,10 +20964,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44910</v>
+        <v>46295</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20989,8 +20979,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21033,7 +21028,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 40528-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21047,10 +21042,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44631</v>
+        <v>46295</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21068,7 +21063,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21111,7 +21106,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 8936-2025</t>
+          <t>A 40335-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21125,10 +21120,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45714</v>
+        <v>46294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21140,8 +21135,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21184,7 +21184,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 40459-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21198,10 +21198,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46253</v>
+        <v>46294</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>46295</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>46295</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46295</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 40336-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21505,10 +21505,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45098</v>
+        <v>46294</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21520,8 +21520,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21564,7 +21569,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21574,14 +21579,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45388</v>
+        <v>44631</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21593,8 +21598,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21637,7 +21647,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 40459-2026</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21651,10 +21661,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46294</v>
+        <v>46253</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21667,7 +21677,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21710,7 +21720,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 40528-2026</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21720,14 +21730,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46295</v>
+        <v>44593</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21741,11 +21751,11 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.5</v>
+        <v>38.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21788,7 +21798,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 40570-2026</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21802,10 +21812,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46295</v>
+        <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21815,11 +21825,6 @@
       <c r="G256" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I256" t="n">
@@ -21866,7 +21871,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 40527-2026</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21880,10 +21885,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46295</v>
+        <v>45158</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21895,13 +21900,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21944,7 +21944,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21958,10 +21958,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45279</v>
+        <v>45457</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21973,13 +21973,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -22022,7 +22017,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -22036,10 +22031,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45252</v>
+        <v>45457</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22052,7 +22047,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -22095,7 +22090,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -22109,10 +22104,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45636</v>
+        <v>45145</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22125,7 +22120,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -22168,7 +22163,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -22182,10 +22177,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44618</v>
+        <v>44550</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22197,8 +22192,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -22241,7 +22241,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 8936-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -22255,10 +22255,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45310</v>
+        <v>45714</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -22331,7 +22331,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>46111</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45388</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45406</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>45617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45457</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45147</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45258</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>46043</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45414</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45091</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45406</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44481</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45187</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45825</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>46076</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45947</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>46021</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44593</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45714</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44957</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>46099</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>45198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>46099</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>46107</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>46107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>46107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46113</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45252</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>46134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46134</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>46134</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45317</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45149</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46134</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45849</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45729</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>45279</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45364</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45246</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45208</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45161</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>46147</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>46147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45939</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>46155</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>46155</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45526</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45310</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44845</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46155</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46155</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45555</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45389</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44958</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45461</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44879</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>46177</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45224</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45414</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45408</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44682</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44859</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45995</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46199</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45091</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45015</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46211</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>46211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46211</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44910</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45758</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46265</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45555</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46265</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>46265</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>46265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>46224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46224</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46268</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44618</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45523</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45147</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>46234</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>46279</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>46276</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>44677</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>46283</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46283</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46283</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45267</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44493</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45370</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45352</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45461</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44534</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46295</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46295</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46295</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>46294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>46294</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>46295</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>46295</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46295</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46294</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44631</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>46253</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44593</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45158</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45457</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45457</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45145</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44550</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45714</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>46013</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44868</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>46111</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45741</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45266</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45388</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45406</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>45617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45457</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45161</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45147</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45638</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45903</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45258</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>46043</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45414</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45091</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44818</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45406</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44481</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44896</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45187</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45825</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>46076</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45947</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>45279</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>46021</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44593</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45714</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44957</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>46099</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>45198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>46099</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45384</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>46107</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45461</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>46107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>46107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>46113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46113</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>44960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45994</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45191</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45994</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45252</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>46134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46134</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>46134</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45317</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45149</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46134</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45849</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45729</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>45279</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45364</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45215</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45246</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45105</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45208</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45161</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45596</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45000</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>46147</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>46147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45740</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45939</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>46155</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>46155</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45526</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45310</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44845</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46155</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46155</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45555</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45389</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44958</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45461</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44879</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>46177</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45224</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45414</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45408</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44682</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>44859</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45995</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46199</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45091</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45015</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46211</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>46211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46211</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44910</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45758</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46265</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45555</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46265</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46265</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>46265</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>46265</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>46224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46224</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46268</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44618</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45523</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45147</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>46234</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>46279</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>46276</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>44677</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>46239</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>46283</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46283</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>46283</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45104</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45267</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44493</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45370</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45352</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45461</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44534</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45070</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46295</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46295</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46295</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>46294</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>46294</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>46295</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>46295</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>46295</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46294</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44631</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>46253</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44593</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>46245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45158</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45457</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45457</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>45145</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>44550</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45714</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45407</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 63537-2025</t>
+          <t>A 33136-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46013</v>
+        <v>45840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,23 +2264,28 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,21 +2294,254 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
       </c>
       <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp
+Tallticka
+Smal svampklubba
+Spillkråka
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 56956-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tretåig hackspett
+Bronshjon
+Gullgröppa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 63537-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="n">
         <v>9</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Mörk husmossa
@@ -2313,270 +2551,32 @@
 Kärrfibbla</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63537-2025 artfynd.xlsx", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63537-2025 karta.png", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63537-2025 georefererad karta.tif", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63537-2025 FSC-klagomål.docx", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63537-2025 FSC-klagomål mail.docx", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63537-2025 tillsynsbegäran.docx", "A 63537-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63537-2025 tillsynsbegäran mail.docx", "A 63537-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56956-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>15</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tretåig hackspett
-Bronshjon
-Gullgröppa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 33136-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45840</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp
-Tallticka
-Smal svampklubba
-Spillkråka
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
         <v/>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39837-2025</t>
+          <t>A 51036-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45891</v>
+        <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,149 +3453,149 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Vårärt
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 39837-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bårdlav
 Stuplav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 51036-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44868</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Vårärt
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2261-2026</t>
+          <t>A 56959-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46036</v>
+        <v>45978</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4082,23 +4082,28 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4110,495 +4115,490 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
       <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56959-2025 artfynd.xlsx", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56959-2025 karta.png", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56959-2025 georefererad karta.tif", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56959-2025 FSC-klagomål.docx", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56959-2025 FSC-klagomål mail.docx", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56959-2025 tillsynsbegäran.docx", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56959-2025 tillsynsbegäran mail.docx", "A 56959-2025")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56959-2025 prioriterade fågelarter.docx", "A 56959-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 16289-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Mindre märgborre
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16289-2026 artfynd.xlsx", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16289-2026 karta.png", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16289-2026 georefererad karta.tif", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16289-2026 FSC-klagomål.docx", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16289-2026 FSC-klagomål mail.docx", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16289-2026 tillsynsbegäran.docx", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16289-2026 tillsynsbegäran mail.docx", "A 16289-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16289-2026 prioriterade fågelarter.docx", "A 16289-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 41696-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 63825-2023</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 2261-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 2261-2026 artfynd.xlsx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 2261-2026 karta.png", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 2261-2026 georefererad karta.tif", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 2261-2026 FSC-klagomål.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 2261-2026 FSC-klagomål mail.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 2261-2026 tillsynsbegäran.docx", "A 2261-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 2261-2026 tillsynsbegäran mail.docx", "A 2261-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 41696-2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 56959-2025</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56959-2025 artfynd.xlsx", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56959-2025 karta.png", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56959-2025 georefererad karta.tif", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56959-2025 FSC-klagomål.docx", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56959-2025 FSC-klagomål mail.docx", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56959-2025 tillsynsbegäran.docx", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56959-2025 tillsynsbegäran mail.docx", "A 56959-2025")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56959-2025 prioriterade fågelarter.docx", "A 56959-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 16289-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Mindre märgborre
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16289-2026 artfynd.xlsx", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16289-2026 karta.png", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16289-2026 georefererad karta.tif", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16289-2026 FSC-klagomål.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16289-2026 FSC-klagomål mail.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16289-2026 tillsynsbegäran.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16289-2026 tillsynsbegäran mail.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16289-2026 prioriterade fågelarter.docx", "A 16289-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 63825-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
         <v/>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45775</v>
+        <v>45741</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5194,22 +5194,22 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5230,46 +5230,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45400</v>
+        <v>45741</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5298,8 +5298,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5308,13 +5313,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
         <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5326,7 +5331,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5335,39 +5340,39 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
@@ -5391,7 +5396,7 @@
         <v>45937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5479,7 +5484,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5489,14 +5494,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45090</v>
+        <v>45177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,8 +5513,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5545,46 +5555,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5598,10 +5608,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45229</v>
+        <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5624,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5623,10 +5633,10 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5641,7 +5651,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5650,39 +5660,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
@@ -5706,7 +5716,7 @@
         <v>45866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5794,7 +5804,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5804,14 +5814,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45741</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5825,11 +5835,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5838,13 +5848,13 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5856,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5865,46 +5875,50 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5918,10 +5932,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45741</v>
+        <v>45775</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5939,7 +5953,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5948,13 +5962,13 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -5966,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5979,42 +5993,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6024,14 +6038,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45177</v>
+        <v>45229</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6043,13 +6057,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6085,39 +6094,39 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
@@ -6141,7 +6150,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6246,7 +6255,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6334,7 +6343,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6348,10 +6357,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45219</v>
+        <v>45090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6363,16 +6372,11 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -6405,50 +6409,46 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 40337-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45027</v>
+        <v>46294</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,8 +6477,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6487,10 +6492,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6514,46 +6519,46 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40337-2026</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6567,10 +6572,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46294</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6582,13 +6587,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6628,35 +6628,35 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44503</v>
+        <v>44791</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44958</v>
+        <v>44834</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44791</v>
+        <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8259,13 +8259,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8308,7 +8303,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8322,10 +8317,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45191</v>
+        <v>45406</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8338,7 +8333,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8381,7 +8376,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8391,14 +8386,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45266</v>
+        <v>45389</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8411,7 +8406,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8454,7 +8449,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8471,7 +8466,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8489,7 +8484,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8532,7 +8527,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8542,14 +8537,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45231</v>
+        <v>44879</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8562,7 +8557,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8605,7 +8600,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8619,10 +8614,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44862</v>
+        <v>44481</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8634,13 +8629,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8683,7 +8673,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8697,10 +8687,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45670</v>
+        <v>44958</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8713,7 +8703,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8756,7 +8746,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8766,14 +8756,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45388</v>
+        <v>45457</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8786,7 +8776,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8829,7 +8819,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8843,10 +8833,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45406</v>
+        <v>45279</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8858,8 +8848,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8902,7 +8897,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8916,10 +8911,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45617</v>
+        <v>44493</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8932,7 +8927,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8975,7 +8970,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8989,10 +8984,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45457</v>
+        <v>44534</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9005,7 +9000,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9048,7 +9043,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45226</v>
+        <v>44889</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9078,7 +9073,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9121,7 +9116,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9135,10 +9130,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45714</v>
+        <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9151,7 +9146,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9194,7 +9189,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9208,10 +9203,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45161</v>
+        <v>45453</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9224,7 +9219,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9267,7 +9262,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9281,10 +9276,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45184</v>
+        <v>46043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9297,7 +9292,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9340,7 +9335,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9354,10 +9349,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45147</v>
+        <v>44862</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9369,8 +9364,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9427,10 +9427,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45166</v>
+        <v>45408</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9442,8 +9442,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9486,7 +9491,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9500,10 +9505,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46034</v>
+        <v>45231</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9516,7 +9521,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9559,7 +9564,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9569,14 +9574,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45638</v>
+        <v>44593</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9588,8 +9593,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>38.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9632,7 +9642,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9646,10 +9656,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45903</v>
+        <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9662,7 +9672,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9705,7 +9715,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9719,10 +9729,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45258</v>
+        <v>45145</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9735,7 +9745,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9778,7 +9788,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9792,10 +9802,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46043</v>
+        <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9808,7 +9818,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9851,7 +9861,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9865,10 +9875,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45414</v>
+        <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9881,7 +9891,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9924,7 +9934,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9938,10 +9948,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45091</v>
+        <v>45849</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9955,11 +9965,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10002,7 +10012,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10012,14 +10022,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45461</v>
+        <v>45364</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10031,8 +10041,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10075,7 +10090,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10089,10 +10104,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45608</v>
+        <v>44859</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10105,7 +10120,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10148,7 +10163,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10162,10 +10177,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44818</v>
+        <v>45191</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10177,13 +10192,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10226,7 +10236,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10240,10 +10250,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45461</v>
+        <v>45226</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10256,7 +10266,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>12.2</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10299,7 +10309,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10313,10 +10323,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45406</v>
+        <v>45191</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10329,7 +10339,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10372,7 +10382,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10386,10 +10396,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45453</v>
+        <v>44677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10402,7 +10412,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10445,7 +10455,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10459,10 +10469,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44481</v>
+        <v>45596</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10474,8 +10484,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10518,7 +10533,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10532,10 +10547,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44896</v>
+        <v>45317</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10547,13 +10562,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10596,7 +10606,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10606,14 +10616,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45187</v>
+        <v>45714</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10625,13 +10635,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10691,7 +10696,7 @@
         <v>45825</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10747,7 +10752,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10757,14 +10762,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45182</v>
+        <v>45939</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10777,7 +10782,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10837,7 +10842,7 @@
         <v>46076</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10898,7 +10903,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10908,14 +10913,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45939</v>
+        <v>45457</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10971,7 +10976,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10985,10 +10990,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45947</v>
+        <v>45457</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11001,7 +11006,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11044,7 +11049,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11058,10 +11063,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45279</v>
+        <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11073,13 +11078,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46021</v>
+        <v>45740</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11195,7 +11195,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11205,14 +11205,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45953</v>
+        <v>44791</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11287,10 +11287,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44593</v>
+        <v>45758</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11346,7 +11346,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45636</v>
+        <v>45184</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11419,7 +11419,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11429,14 +11429,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45714</v>
+        <v>45953</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11448,8 +11448,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11492,7 +11497,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11506,10 +11511,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44957</v>
+        <v>45147</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11522,7 +11527,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11565,7 +11570,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11579,10 +11584,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45965</v>
+        <v>46021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11595,7 +11600,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11638,7 +11643,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11652,10 +11657,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46099</v>
+        <v>45225</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11668,7 +11673,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11711,7 +11716,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11725,10 +11730,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45198</v>
+        <v>46099</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11741,7 +11746,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11784,7 +11789,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11798,10 +11803,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46099</v>
+        <v>45965</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11814,7 +11819,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11857,7 +11862,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11871,10 +11876,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45384</v>
+        <v>45091</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11886,8 +11891,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11930,7 +11940,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11944,10 +11954,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46107</v>
+        <v>45161</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11960,7 +11970,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12003,7 +12013,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12017,10 +12027,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45461</v>
+        <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12033,7 +12043,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12076,7 +12086,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12090,10 +12100,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46107</v>
+        <v>44845</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12106,7 +12116,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12166,7 +12176,7 @@
         <v>46107</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12222,7 +12232,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12236,10 +12246,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45985</v>
+        <v>46107</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12252,7 +12262,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12295,7 +12305,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12309,10 +12319,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12324,13 +12334,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12373,7 +12378,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12390,7 +12395,7 @@
         <v>46113</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12408,7 +12413,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12451,7 +12456,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12468,7 +12473,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12486,7 +12491,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12529,7 +12534,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12546,7 +12551,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12564,7 +12569,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12607,7 +12612,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12621,10 +12626,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44960</v>
+        <v>46113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12638,11 +12643,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12685,7 +12690,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12702,7 +12707,7 @@
         <v>46113</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12720,7 +12725,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12763,7 +12768,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12780,7 +12785,7 @@
         <v>46113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12798,7 +12803,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12841,7 +12846,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12858,7 +12863,7 @@
         <v>46113</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12919,7 +12924,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12933,10 +12938,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45994</v>
+        <v>45555</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12949,7 +12954,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12992,7 +12997,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13006,10 +13011,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45191</v>
+        <v>45985</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13022,7 +13027,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13065,7 +13070,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13079,10 +13084,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45994</v>
+        <v>45070</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13095,7 +13100,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13138,7 +13143,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13152,10 +13157,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45252</v>
+        <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13168,7 +13173,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13211,7 +13216,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13225,10 +13230,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46134</v>
+        <v>45994</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13240,13 +13245,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13289,7 +13289,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13306,7 +13306,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13367,7 +13367,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13384,7 +13384,7 @@
         <v>46134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13445,7 +13445,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13462,7 +13462,7 @@
         <v>46134</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13523,7 +13523,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13540,7 +13540,7 @@
         <v>46134</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13601,7 +13601,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13618,7 +13618,7 @@
         <v>46134</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13679,7 +13679,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13696,7 +13696,7 @@
         <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 19510-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13774,7 +13774,7 @@
         <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13835,7 +13835,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 19512-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45317</v>
+        <v>46134</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13864,8 +13864,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13908,7 +13913,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13922,10 +13927,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45196</v>
+        <v>46134</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13937,8 +13942,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>8.800000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13981,7 +13991,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13995,10 +14005,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45149</v>
+        <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14011,7 +14021,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14054,7 +14064,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14068,10 +14078,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46134</v>
+        <v>45104</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14083,13 +14093,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14132,7 +14137,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14146,10 +14151,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44834</v>
+        <v>45258</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14162,7 +14167,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14205,7 +14210,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14219,10 +14224,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45849</v>
+        <v>45161</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14234,13 +14239,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14283,7 +14283,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14293,14 +14293,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45532</v>
+        <v>45370</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14312,8 +14312,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14356,7 +14361,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14370,10 +14375,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45729</v>
+        <v>45015</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14386,7 +14391,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14429,7 +14434,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14443,10 +14448,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45279</v>
+        <v>46034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14458,13 +14463,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14507,7 +14507,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45191</v>
+        <v>45352</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14580,7 +14580,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14590,14 +14590,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45364</v>
+        <v>44818</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14672,10 +14672,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45215</v>
+        <v>45729</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14731,7 +14731,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14745,10 +14745,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45246</v>
+        <v>45461</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14760,13 +14760,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14809,7 +14804,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14823,10 +14818,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45755</v>
+        <v>45246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14838,8 +14833,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14882,7 +14882,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14892,14 +14892,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45105</v>
+        <v>45532</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14955,7 +14955,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14969,10 +14969,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45208</v>
+        <v>45000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14984,8 +14984,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15028,7 +15033,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15042,10 +15047,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44791</v>
+        <v>45191</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15057,13 +15062,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45161</v>
+        <v>45384</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15179,7 +15179,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15193,10 +15193,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45596</v>
+        <v>46147</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15257,7 +15257,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15274,7 +15274,7 @@
         <v>46147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15335,7 +15335,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45000</v>
+        <v>46147</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15413,7 +15413,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15430,7 +15430,7 @@
         <v>46147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15508,7 +15508,7 @@
         <v>46147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15579,14 +15579,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46147</v>
+        <v>45939</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15598,13 +15598,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15647,7 +15642,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15661,10 +15656,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15682,7 +15677,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15725,7 +15720,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15739,10 +15734,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45740</v>
+        <v>46155</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15754,8 +15749,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15798,7 +15798,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45929</v>
+        <v>45526</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15827,8 +15827,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15871,7 +15876,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15881,14 +15886,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45939</v>
+        <v>46155</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15900,8 +15905,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15944,7 +15954,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15961,7 +15971,7 @@
         <v>46155</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15979,7 +15989,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16022,7 +16032,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16036,10 +16046,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46155</v>
+        <v>45929</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16051,13 +16061,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16100,7 +16105,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16117,7 +16122,7 @@
         <v>46155</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16135,7 +16140,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16178,7 +16183,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16195,7 +16200,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16213,7 +16218,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16256,7 +16261,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16270,10 +16275,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45526</v>
+        <v>46155</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16287,11 +16292,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16334,7 +16339,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16348,10 +16353,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46154</v>
+        <v>44550</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16369,7 +16374,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16412,7 +16417,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16426,10 +16431,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45310</v>
+        <v>45555</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16442,7 +16447,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16485,7 +16490,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16495,14 +16500,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44845</v>
+        <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16514,8 +16519,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16558,7 +16568,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16572,10 +16582,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46155</v>
+        <v>45158</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16587,13 +16597,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16636,7 +16641,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16650,10 +16655,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46155</v>
+        <v>45215</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16665,13 +16670,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16714,7 +16714,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45555</v>
+        <v>45149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16787,7 +16787,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16801,10 +16801,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45098</v>
+        <v>45198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16870,14 +16870,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45389</v>
+        <v>46177</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16933,7 +16933,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44958</v>
+        <v>45714</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17020,10 +17020,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45461</v>
+        <v>44682</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17089,14 +17089,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44879</v>
+        <v>45166</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46177</v>
+        <v>45461</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.3</v>
+        <v>9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17225,7 +17225,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45224</v>
+        <v>45995</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17298,7 +17298,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17312,10 +17312,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45414</v>
+        <v>45267</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17371,7 +17371,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45408</v>
+        <v>44503</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17400,13 +17400,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17449,7 +17444,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17463,10 +17458,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44682</v>
+        <v>46199</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17479,7 +17474,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17522,7 +17517,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17536,10 +17531,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44859</v>
+        <v>45755</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17552,7 +17547,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17595,7 +17590,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17609,10 +17604,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45995</v>
+        <v>45091</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17624,8 +17619,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17668,7 +17668,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17682,10 +17682,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46199</v>
+        <v>44896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17697,8 +17697,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17741,7 +17746,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17755,10 +17760,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44889</v>
+        <v>45208</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17771,7 +17776,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17814,7 +17819,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17828,10 +17833,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45091</v>
+        <v>46211</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17843,13 +17848,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17906,10 +17906,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45015</v>
+        <v>46211</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17965,7 +17965,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17979,10 +17979,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45191</v>
+        <v>46211</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18038,7 +18038,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18052,10 +18052,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46211</v>
+        <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18111,7 +18111,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18128,7 +18128,7 @@
         <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46211</v>
+        <v>45461</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7.3</v>
+        <v>2.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45901</v>
+        <v>44791</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18286,8 +18286,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18330,7 +18335,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18344,10 +18349,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46211</v>
+        <v>46265</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18359,8 +18364,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18403,7 +18413,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18417,10 +18427,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44910</v>
+        <v>46265</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18432,8 +18442,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18476,7 +18491,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18490,10 +18505,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45758</v>
+        <v>46265</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18505,8 +18520,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18549,7 +18569,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18566,7 +18586,7 @@
         <v>46265</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18584,7 +18604,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18627,7 +18647,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18641,10 +18661,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45555</v>
+        <v>46265</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18656,8 +18676,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18700,7 +18725,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18714,10 +18739,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18729,13 +18754,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18778,7 +18798,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18792,10 +18812,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46265</v>
+        <v>45224</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18807,13 +18827,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18856,7 +18871,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18870,10 +18885,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18885,13 +18900,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18934,7 +18944,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18948,10 +18958,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46265</v>
+        <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18965,11 +18975,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19029,7 +19039,7 @@
         <v>46224</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19085,7 +19095,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19099,10 +19109,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46224</v>
+        <v>45147</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19115,7 +19125,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19158,7 +19168,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19172,10 +19182,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46268</v>
+        <v>46276</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19187,8 +19197,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19231,7 +19246,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19245,10 +19260,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44618</v>
+        <v>45461</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19261,7 +19276,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.8</v>
+        <v>12.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19304,7 +19319,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19318,10 +19333,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45523</v>
+        <v>45266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19377,7 +19392,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19391,10 +19406,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45147</v>
+        <v>46279</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19407,7 +19422,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19450,7 +19465,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19464,10 +19479,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46234</v>
+        <v>45414</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19480,7 +19495,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19523,7 +19538,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19537,10 +19552,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46279</v>
+        <v>46234</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19553,7 +19568,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19596,7 +19611,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19610,10 +19625,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19631,7 +19646,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19674,7 +19689,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19688,10 +19703,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44677</v>
+        <v>45638</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19704,7 +19719,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19747,7 +19762,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19761,10 +19776,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19782,7 +19797,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19825,7 +19840,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19839,10 +19854,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46239</v>
+        <v>44958</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19854,13 +19869,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19903,7 +19913,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19917,10 +19927,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44791</v>
+        <v>45523</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19933,7 +19943,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19976,7 +19986,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19993,7 +20003,7 @@
         <v>46283</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20011,7 +20021,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20054,7 +20064,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20068,10 +20078,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46283</v>
+        <v>45105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20083,13 +20093,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20132,7 +20137,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20146,10 +20151,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46283</v>
+        <v>45461</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20161,13 +20166,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20224,10 +20224,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45225</v>
+        <v>45182</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20283,7 +20283,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20297,10 +20297,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45104</v>
+        <v>45191</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20356,7 +20356,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20370,10 +20370,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45267</v>
+        <v>44910</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20429,7 +20429,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20443,10 +20443,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44493</v>
+        <v>44631</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20458,8 +20458,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20502,7 +20507,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 8936-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20516,10 +20521,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45370</v>
+        <v>45714</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20531,13 +20536,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20580,7 +20580,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20594,10 +20594,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45352</v>
+        <v>46283</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20609,8 +20609,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20653,7 +20658,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20667,10 +20672,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45461</v>
+        <v>46283</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20682,8 +20687,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20726,7 +20736,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20740,10 +20750,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44534</v>
+        <v>45098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20756,7 +20766,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20799,7 +20809,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20809,14 +20819,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45070</v>
+        <v>45388</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20829,7 +20839,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20872,7 +20882,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 40527-2026</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20886,10 +20896,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46295</v>
+        <v>45279</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20907,7 +20917,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20950,7 +20960,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 40570-2026</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20964,10 +20974,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46295</v>
+        <v>45252</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20979,13 +20989,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21028,7 +21033,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 40528-2026</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21042,10 +21047,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46295</v>
+        <v>45636</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21057,13 +21062,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21106,7 +21106,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 40335-2026</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21120,10 +21120,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46294</v>
+        <v>44618</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21135,13 +21135,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21184,7 +21179,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 40459-2026</t>
+          <t>A 40336-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21201,7 +21196,7 @@
         <v>46294</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21213,8 +21208,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21257,7 +21257,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 40525-2026</t>
+          <t>A 40335-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21271,10 +21271,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21335,7 +21335,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 40532-2026</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21349,10 +21349,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46295</v>
+        <v>45310</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21364,13 +21364,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21413,7 +21408,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 40533-2026</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21427,10 +21422,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46295</v>
+        <v>46253</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21442,13 +21437,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21491,7 +21481,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 40336-2026</t>
+          <t>A 40525-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21505,10 +21495,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21526,7 +21516,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21569,7 +21559,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 40532-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21583,10 +21573,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44631</v>
+        <v>46295</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21604,7 +21594,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21647,7 +21637,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 40533-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21661,10 +21651,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46253</v>
+        <v>46295</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21676,8 +21666,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21720,7 +21715,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 40459-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21730,14 +21725,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44593</v>
+        <v>46294</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21749,13 +21744,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>38.4</v>
+        <v>0.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21798,7 +21788,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 40528-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21812,10 +21802,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46245</v>
+        <v>46295</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21827,8 +21817,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21871,7 +21866,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 40570-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21885,10 +21880,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45158</v>
+        <v>46295</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21900,8 +21895,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21944,7 +21944,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 16281-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21958,10 +21958,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45457</v>
+        <v>45407</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -22017,7 +22017,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 40527-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -22031,10 +22031,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45457</v>
+        <v>46295</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22046,8 +22046,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -22090,7 +22095,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -22104,10 +22109,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45145</v>
+        <v>45670</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22120,7 +22125,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -22163,7 +22168,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -22177,10 +22182,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44550</v>
+        <v>46245</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22192,13 +22197,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -22241,7 +22241,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 8936-2025</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -22255,10 +22255,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45714</v>
+        <v>45617</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -22314,7 +22314,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 16281-2024</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -22328,10 +22328,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -22404,7 +22404,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33136-2025</t>
+          <t>A 56956-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45840</v>
+        <v>45978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>22.2</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -2303,12 +2303,131 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
+        <v>15</v>
+      </c>
+      <c r="U15" t="n">
+        <v>15</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tretåig hackspett
+Bronshjon
+Gullgröppa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 33136-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45840</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Orange taggsvamp
 Tallticka
@@ -2318,155 +2437,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56956-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>15</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tretåig hackspett
-Bronshjon
-Gullgröppa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
         <v/>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51036-2022</t>
+          <t>A 39837-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44868</v>
+        <v>45891</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,149 +3453,149 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Bårdlav
+Stuplav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 51036-2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>44868</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Loppstarr
 Vårärt
 Blåmossa</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 39837-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45891</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav
-Stuplav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
         <v/>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56959-2025</t>
+          <t>A 2261-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45978</v>
+        <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4082,28 +4082,23 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4115,490 +4110,495 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
       <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 2261-2026 artfynd.xlsx", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 2261-2026 karta.png", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 2261-2026 georefererad karta.tif", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 2261-2026 FSC-klagomål.docx", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 2261-2026 FSC-klagomål mail.docx", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 2261-2026 tillsynsbegäran.docx", "A 2261-2026")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 2261-2026 tillsynsbegäran mail.docx", "A 2261-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 41696-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45176</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Järpe
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 56959-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56959-2025 artfynd.xlsx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56959-2025 karta.png", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56959-2025 georefererad karta.tif", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56959-2025 FSC-klagomål.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56959-2025 FSC-klagomål mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56959-2025 tillsynsbegäran.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56959-2025 tillsynsbegäran mail.docx", "A 56959-2025")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56959-2025 prioriterade fågelarter.docx", "A 56959-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 16289-2026</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>46111</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Mindre märgborre
 Spillkråka</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16289-2026 artfynd.xlsx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16289-2026 karta.png", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16289-2026 georefererad karta.tif", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16289-2026 FSC-klagomål.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16289-2026 FSC-klagomål mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16289-2026 tillsynsbegäran.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16289-2026 tillsynsbegäran mail.docx", "A 16289-2026")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 16289-2026 prioriterade fågelarter.docx", "A 16289-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 41696-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45176</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J33" t="n">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 63825-2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
-        <v>2</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Järpe
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 41696-2023 artfynd.xlsx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 41696-2023 karta.png", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 41696-2023 georefererad karta.tif", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 41696-2023 FSC-klagomål.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 41696-2023 FSC-klagomål mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 41696-2023 tillsynsbegäran.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 41696-2023 tillsynsbegäran mail.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 41696-2023 prioriterade fågelarter.docx", "A 41696-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 63825-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45278</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Skogsödla</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 63825-2023 artfynd.xlsx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 63825-2023 karta.png", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 63825-2023 georefererad karta.tif", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 63825-2023 FSC-klagomål.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 63825-2023 FSC-klagomål mail.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 63825-2023 tillsynsbegäran.docx", "A 63825-2023")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 63825-2023 tillsynsbegäran mail.docx", "A 63825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 2261-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46036</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Flodpärlmussla
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 2261-2026 artfynd.xlsx", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 2261-2026 karta.png", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 2261-2026 georefererad karta.tif", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 2261-2026 FSC-klagomål.docx", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 2261-2026 FSC-klagomål mail.docx", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 2261-2026 tillsynsbegäran.docx", "A 2261-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 2261-2026 tillsynsbegäran mail.docx", "A 2261-2026")</f>
         <v/>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45741</v>
+        <v>45775</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5194,22 +5194,22 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5221,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5230,46 +5230,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45741</v>
+        <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5298,13 +5298,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5313,13 +5308,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5331,7 +5326,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5340,46 +5335,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5393,10 +5388,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45937</v>
+        <v>45090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5409,17 +5404,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5433,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5449,42 +5444,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5494,14 +5489,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45177</v>
+        <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5513,13 +5508,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5555,46 +5545,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5608,10 +5598,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45027</v>
+        <v>45937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,19 +5614,19 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5648,10 +5638,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5660,46 +5650,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5709,14 +5699,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45866</v>
+        <v>45741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,8 +5718,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5744,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5753,10 +5748,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5769,42 +5764,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5814,14 +5809,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45741</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5835,26 +5830,26 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
         <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5866,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5879,46 +5874,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5928,14 +5919,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45775</v>
+        <v>45866</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5947,22 +5938,17 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5977,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5989,46 +5975,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6038,14 +6024,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45229</v>
+        <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6057,8 +6043,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6094,39 +6085,39 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
@@ -6150,7 +6141,7 @@
         <v>46210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6246,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6334,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6357,10 +6348,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45090</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,11 +6363,16 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -6409,46 +6405,50 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE52">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40337-2026</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46294</v>
+        <v>45027</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,13 +6477,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6492,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6510,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6519,46 +6514,46 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 40337-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6572,10 +6567,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6587,8 +6582,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6628,35 +6628,35 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 40337-2026 artfynd.xlsx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 40337-2026 karta.png", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 40337-2026 georefererad karta.tif", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 40337-2026 FSC-klagomål.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 40337-2026 FSC-klagomål mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 40337-2026 tillsynsbegäran.docx", "A 40337-2026")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 40337-2026 tillsynsbegäran mail.docx", "A 40337-2026")</f>
         <v/>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44876</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44560</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44807</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44791</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44714</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44841</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44799</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44491</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44530</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34026-2022</t>
+          <t>A 62592-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44791</v>
+        <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44834</v>
+        <v>44958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 34164-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45196</v>
+        <v>44791</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8259,8 +8259,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8303,7 +8308,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8317,10 +8322,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45406</v>
+        <v>45191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8333,7 +8338,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8376,7 +8381,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13585-2024</t>
+          <t>A 26023-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8386,14 +8391,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45389</v>
+        <v>45091</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8405,8 +8410,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8449,7 +8459,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 61952-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8463,10 +8473,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45091</v>
+        <v>45266</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8478,13 +8488,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8527,7 +8532,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53472-2022</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8537,14 +8542,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44879</v>
+        <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8557,7 +8562,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8600,7 +8605,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56871-2021</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8614,10 +8619,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44481</v>
+        <v>45406</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8630,7 +8635,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8673,7 +8678,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 13563-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8683,14 +8688,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44958</v>
+        <v>45388</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8703,7 +8708,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8763,7 +8768,7 @@
         <v>45457</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8819,7 +8824,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64089-2023</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8833,10 +8838,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45279</v>
+        <v>45226</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8848,13 +8853,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59637-2021</t>
+          <t>A 9457-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44493</v>
+        <v>45714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 70200-2021</t>
+          <t>A 35675-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44534</v>
+        <v>45147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56136-2022</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44889</v>
+        <v>45161</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52303-2024</t>
+          <t>A 39257-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45608</v>
+        <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45453</v>
+        <v>45184</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 59607-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9276,10 +9276,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46043</v>
+        <v>45638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9335,7 +9335,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44862</v>
+        <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9364,13 +9364,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9413,7 +9408,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16557-2024</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9427,10 +9422,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45408</v>
+        <v>45091</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9444,11 +9439,11 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9491,7 +9486,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9505,10 +9500,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45231</v>
+        <v>44862</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9520,8 +9515,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5217-2022</t>
+          <t>A 24820-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9574,14 +9574,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44593</v>
+        <v>45461</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9593,13 +9593,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>38.4</v>
+        <v>5.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9642,7 +9637,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9656,10 +9651,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44957</v>
+        <v>46034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9672,7 +9667,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9715,7 +9710,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35144-2023</t>
+          <t>A 39707-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9729,10 +9724,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45145</v>
+        <v>44818</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9744,8 +9739,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9788,7 +9788,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 24821-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9802,10 +9802,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45903</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9861,7 +9861,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44593</v>
+        <v>45406</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 52303-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9948,10 +9948,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45849</v>
+        <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9963,13 +9963,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10012,7 +10007,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10079-2024</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10022,14 +10017,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45364</v>
+        <v>46043</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10041,13 +10036,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10090,7 +10080,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48707-2022</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10104,10 +10094,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44859</v>
+        <v>45453</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10120,7 +10110,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10163,7 +10153,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 56871-2021</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10177,10 +10167,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45191</v>
+        <v>44481</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10193,7 +10183,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10236,7 +10226,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 57316-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10250,10 +10240,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45226</v>
+        <v>44896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10265,8 +10255,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10309,7 +10304,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 43843-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10319,14 +10314,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45191</v>
+        <v>45187</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10338,8 +10333,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17140-2022</t>
+          <t>A 43919-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44677</v>
+        <v>45182</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49498-2024</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10469,10 +10469,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45596</v>
+        <v>45903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10484,13 +10484,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10533,7 +10528,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 64090-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10547,10 +10542,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45317</v>
+        <v>45279</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10562,8 +10557,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10620,10 +10620,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45714</v>
+        <v>46076</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10635,8 +10635,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10679,7 +10684,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 29669-2025</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10693,10 +10698,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45825</v>
+        <v>44593</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10709,7 +10714,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10752,7 +10757,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 59056-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10762,14 +10767,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45939</v>
+        <v>45636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10782,7 +10787,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10825,7 +10830,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 64026-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10839,10 +10844,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46076</v>
+        <v>46021</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10854,13 +10859,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10903,7 +10903,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24391-2024</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10917,10 +10917,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45457</v>
+        <v>45714</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24392-2024</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45457</v>
+        <v>44957</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11049,7 +11049,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 46688-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11063,10 +11063,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45947</v>
+        <v>45198</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14315-2025</t>
+          <t>A 12646-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45740</v>
+        <v>45384</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11195,7 +11195,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 34206-2022</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11209,10 +11209,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44791</v>
+        <v>46099</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11224,13 +11224,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11273,7 +11268,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17716-2025</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11287,10 +11282,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45758</v>
+        <v>46099</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11303,7 +11298,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11346,7 +11341,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 24822-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11360,10 +11355,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45184</v>
+        <v>45461</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11376,7 +11371,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11419,7 +11414,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 29669-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11429,14 +11424,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45953</v>
+        <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11448,13 +11443,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11497,7 +11487,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35659-2023</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11511,10 +11501,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45147</v>
+        <v>45849</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11526,8 +11516,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11570,7 +11565,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 64026-2025</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11584,10 +11579,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46021</v>
+        <v>46107</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11600,7 +11595,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11643,7 +11638,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52505-2023</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11653,14 +11648,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45225</v>
+        <v>45939</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11673,7 +11668,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11716,7 +11711,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11730,10 +11725,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11746,7 +11741,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11789,7 +11784,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11803,10 +11798,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45965</v>
+        <v>45947</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11819,7 +11814,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11862,7 +11857,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26022-2023</t>
+          <t>A 5674-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11876,10 +11871,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45091</v>
+        <v>44960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11897,7 +11892,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11940,7 +11935,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11954,10 +11949,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45161</v>
+        <v>46107</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11970,7 +11965,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12013,7 +12008,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12027,10 +12022,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46099</v>
+        <v>46113</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12042,8 +12037,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12086,7 +12086,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 45645-2022</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44845</v>
+        <v>46113</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12115,8 +12115,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12159,7 +12164,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12173,10 +12178,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12188,8 +12193,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12232,7 +12242,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 16810-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12246,10 +12256,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12261,8 +12271,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12305,7 +12320,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12315,14 +12330,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46107</v>
+        <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12334,8 +12349,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12378,7 +12398,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12395,7 +12415,7 @@
         <v>46113</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12413,7 +12433,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12456,7 +12476,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12473,7 +12493,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12491,7 +12511,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12534,7 +12554,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12551,7 +12571,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12569,7 +12589,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12612,7 +12632,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16810-2026</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12626,10 +12646,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46113</v>
+        <v>45596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12647,7 +12667,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12690,7 +12710,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12704,10 +12724,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46113</v>
+        <v>45191</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12719,13 +12739,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12768,7 +12783,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12782,10 +12797,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46113</v>
+        <v>45965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12797,13 +12812,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12846,7 +12856,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12860,10 +12870,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12881,7 +12891,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12924,7 +12934,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 40497-2024</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12938,10 +12948,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45555</v>
+        <v>46134</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12953,8 +12963,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12997,7 +13012,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 19510-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13011,10 +13026,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45985</v>
+        <v>46134</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13026,8 +13041,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13070,7 +13090,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22389-2023</t>
+          <t>A 19512-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13084,10 +13104,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45070</v>
+        <v>46134</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13099,8 +13119,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13143,7 +13168,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13157,10 +13182,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45994</v>
+        <v>46134</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13172,8 +13197,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13216,7 +13246,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13230,10 +13260,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45994</v>
+        <v>46134</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13245,8 +13275,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13289,7 +13324,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13306,7 +13341,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13324,7 +13359,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13367,7 +13402,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 19509-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13384,7 +13419,7 @@
         <v>46134</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13402,7 +13437,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13445,7 +13480,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 19553-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13462,7 +13497,7 @@
         <v>46134</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13480,7 +13515,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13523,7 +13558,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 58829-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13537,10 +13572,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46134</v>
+        <v>45252</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13552,13 +13587,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13601,7 +13631,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13615,10 +13645,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46134</v>
+        <v>45317</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13630,13 +13660,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13679,7 +13704,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13693,10 +13718,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46134</v>
+        <v>45196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13708,13 +13733,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13757,7 +13777,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 36064-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13771,10 +13791,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46134</v>
+        <v>45149</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13786,13 +13806,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13835,7 +13850,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13849,10 +13864,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46134</v>
+        <v>44834</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13864,13 +13879,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13913,7 +13923,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13927,10 +13937,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46134</v>
+        <v>45985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13942,13 +13952,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13991,7 +13996,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 35656-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14001,14 +14006,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45406</v>
+        <v>45532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14021,7 +14026,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14064,7 +14069,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 29018-2023</t>
+          <t>A 12183-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14078,10 +14083,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45104</v>
+        <v>45729</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14094,7 +14099,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14137,7 +14142,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14151,10 +14156,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45258</v>
+        <v>45994</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14167,7 +14172,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14210,7 +14215,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 38177-2023</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14224,10 +14229,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45161</v>
+        <v>45994</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14240,7 +14245,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14283,7 +14288,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10882-2024</t>
+          <t>A 21262-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14297,10 +14302,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45370</v>
+        <v>46147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14318,7 +14323,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14361,7 +14366,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 15012-2023</t>
+          <t>A 21271-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14375,10 +14380,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45015</v>
+        <v>46147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14390,8 +14395,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14434,7 +14444,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 21276-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14448,10 +14458,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46034</v>
+        <v>46147</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14463,8 +14473,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14507,7 +14522,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8295-2024</t>
+          <t>A 21256-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14521,10 +14536,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45352</v>
+        <v>46147</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14536,8 +14551,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14580,7 +14600,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 21270-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14594,10 +14614,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44818</v>
+        <v>46147</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14615,7 +14635,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14658,7 +14678,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12183-2025</t>
+          <t>A 47030-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14672,10 +14692,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45729</v>
+        <v>45929</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14688,7 +14708,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14731,7 +14751,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 49676-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14741,14 +14761,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45461</v>
+        <v>45939</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14781,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14804,7 +14824,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 57639-2023</t>
+          <t>A 22474-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14818,10 +14838,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45246</v>
+        <v>46155</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14859,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14882,7 +14902,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 22478-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14892,14 +14912,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45532</v>
+        <v>46155</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14909,6 +14929,11 @@
       <c r="G164" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -14955,7 +14980,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 12699-2023</t>
+          <t>A 22481-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14969,10 +14994,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45000</v>
+        <v>46155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14990,7 +15015,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>5.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15033,7 +15058,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 45234-2023</t>
+          <t>A 22480-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15047,10 +15072,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45191</v>
+        <v>46155</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15062,8 +15087,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15106,7 +15136,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 34759-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15120,10 +15150,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45384</v>
+        <v>45526</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15135,8 +15165,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>8.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15179,7 +15214,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21262-2026</t>
+          <t>A 22266-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15193,10 +15228,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15257,7 +15292,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21271-2026</t>
+          <t>A 22476-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15271,10 +15306,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15292,7 +15327,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15335,7 +15370,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21256-2026</t>
+          <t>A 22485-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15349,10 +15384,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15370,7 +15405,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15413,7 +15448,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21270-2026</t>
+          <t>A 25486-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15427,10 +15462,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46147</v>
+        <v>46177</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15442,13 +15477,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15491,7 +15521,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21276-2026</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15505,10 +15535,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46147</v>
+        <v>45279</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15526,7 +15556,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15569,7 +15599,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 49676-2025</t>
+          <t>A 45229-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15579,14 +15609,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45939</v>
+        <v>45191</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15599,7 +15629,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15642,7 +15672,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22266-2026</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15652,14 +15682,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46154</v>
+        <v>45364</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15677,7 +15707,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15720,7 +15750,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22480-2026</t>
+          <t>A 49959-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15734,10 +15764,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46155</v>
+        <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15749,13 +15779,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15798,7 +15823,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34759-2024</t>
+          <t>A 57639-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15812,10 +15837,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45526</v>
+        <v>45246</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15829,11 +15854,11 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15876,7 +15901,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 22476-2026</t>
+          <t>A 16957-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15890,10 +15915,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46155</v>
+        <v>45755</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15905,13 +15930,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15954,7 +15974,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 22485-2026</t>
+          <t>A 29112-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15968,10 +15988,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46155</v>
+        <v>45105</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15983,13 +16003,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16032,7 +16047,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 47030-2025</t>
+          <t>A 48610-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16046,10 +16061,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45929</v>
+        <v>45208</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16062,7 +16077,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16105,7 +16120,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 22474-2026</t>
+          <t>A 60548-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16119,10 +16134,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46155</v>
+        <v>45995</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16134,13 +16149,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16183,7 +16193,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 22478-2026</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16197,10 +16207,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46155</v>
+        <v>44791</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16218,7 +16228,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16261,7 +16271,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22481-2026</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16275,10 +16285,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46155</v>
+        <v>45161</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16290,13 +16300,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16339,7 +16344,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 73009-2021</t>
+          <t>A 29081-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16353,10 +16358,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44550</v>
+        <v>46199</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16368,13 +16373,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16417,7 +16417,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 40339-2024</t>
+          <t>A 12699-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16431,10 +16431,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45555</v>
+        <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16446,8 +16446,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16490,7 +16495,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16500,14 +16505,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45187</v>
+        <v>45740</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16519,13 +16524,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16568,7 +16568,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37849-2023</t>
+          <t>A 2413-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16582,10 +16582,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45158</v>
+        <v>45310</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16641,7 +16641,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 49959-2023</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16655,10 +16655,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45215</v>
+        <v>44845</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16714,7 +16714,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16728,10 +16728,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45149</v>
+        <v>45555</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16787,7 +16787,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 27767-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16801,10 +16801,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45198</v>
+        <v>45098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 25486-2026</t>
+          <t>A 30690-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16874,10 +16874,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46177</v>
+        <v>46211</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16933,7 +16933,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 30648-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16947,10 +16947,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45714</v>
+        <v>46211</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 17770-2022</t>
+          <t>A 30649-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17020,10 +17020,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44682</v>
+        <v>46211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>7.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17079,7 +17079,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17089,14 +17089,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45166</v>
+        <v>45389</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17152,7 +17152,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24818-2024</t>
+          <t>A 41588-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45461</v>
+        <v>45901</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17225,7 +17225,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 60548-2025</t>
+          <t>A 30655-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45995</v>
+        <v>46211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17298,7 +17298,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 62217-2023</t>
+          <t>A 4977-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17312,10 +17312,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45267</v>
+        <v>44958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17371,7 +17371,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 35627-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17385,10 +17385,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44503</v>
+        <v>46265</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17400,8 +17400,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17444,7 +17449,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 29081-2026</t>
+          <t>A 24818-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17458,10 +17463,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46199</v>
+        <v>45461</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17474,7 +17479,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17517,7 +17522,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 16957-2025</t>
+          <t>A 35631-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17531,10 +17536,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45755</v>
+        <v>46265</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17546,8 +17551,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17590,7 +17600,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 35632-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17604,10 +17614,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45091</v>
+        <v>46265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17621,11 +17631,11 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17668,7 +17678,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 35633-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17682,10 +17692,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44896</v>
+        <v>46265</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17703,7 +17713,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17746,7 +17756,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 48610-2023</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17756,14 +17766,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45208</v>
+        <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17776,7 +17786,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17819,7 +17829,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30655-2026</t>
+          <t>A 35634-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17833,10 +17843,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46211</v>
+        <v>46265</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17848,8 +17858,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17892,7 +17907,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30648-2026</t>
+          <t>A 31579-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17906,10 +17921,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17922,7 +17937,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17965,7 +17980,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 30649-2026</t>
+          <t>A 52379-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17979,10 +17994,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46211</v>
+        <v>45224</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17995,7 +18010,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18038,7 +18053,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 41588-2025</t>
+          <t>A 31578-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18052,10 +18067,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45901</v>
+        <v>46224</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18068,7 +18083,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18111,7 +18126,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30690-2026</t>
+          <t>A 17352-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18125,10 +18140,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46211</v>
+        <v>45414</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18141,7 +18156,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18184,7 +18199,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 24832-2024</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18198,10 +18213,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45461</v>
+        <v>45408</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18213,8 +18228,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18257,7 +18277,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 17770-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18271,10 +18291,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44791</v>
+        <v>44682</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18286,13 +18306,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18335,7 +18350,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35632-2026</t>
+          <t>A 36309-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18349,10 +18364,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18364,13 +18379,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18413,7 +18423,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35631-2026</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18427,10 +18437,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46265</v>
+        <v>44859</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18442,13 +18452,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18491,7 +18496,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35633-2026</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18505,10 +18510,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46265</v>
+        <v>44889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18520,13 +18525,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18569,7 +18569,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 35634-2026</t>
+          <t>A 32130-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18583,10 +18583,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18598,13 +18598,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18647,7 +18642,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35627-2026</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18661,10 +18656,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46265</v>
+        <v>45091</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18678,11 +18673,11 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18725,7 +18720,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36309-2026</t>
+          <t>A 37877-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18739,10 +18734,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18755,7 +18750,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18798,7 +18793,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 52379-2023</t>
+          <t>A 15012-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18812,10 +18807,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45224</v>
+        <v>45015</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18828,7 +18823,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18871,7 +18866,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31578-2026</t>
+          <t>A 45234-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18885,10 +18880,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46224</v>
+        <v>45191</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18901,7 +18896,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18944,7 +18939,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 37504-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18958,10 +18953,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44960</v>
+        <v>46276</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18975,11 +18970,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19022,7 +19017,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31579-2026</t>
+          <t>A 60397-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19036,10 +19031,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46224</v>
+        <v>44910</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19052,7 +19047,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19095,7 +19090,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19109,10 +19104,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45147</v>
+        <v>45758</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19125,7 +19120,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19168,7 +19163,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37504-2026</t>
+          <t>A 38209-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19182,10 +19177,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19203,7 +19198,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19246,7 +19241,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 32432-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19260,10 +19255,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45461</v>
+        <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19275,8 +19270,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>12.2</v>
+        <v>5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19319,7 +19319,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 38674-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19333,10 +19333,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45266</v>
+        <v>46283</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19348,8 +19348,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19392,7 +19397,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37877-2026</t>
+          <t>A 38673-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19406,10 +19411,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19421,8 +19426,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19465,7 +19475,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 17352-2024</t>
+          <t>A 38676-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19479,10 +19489,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45414</v>
+        <v>46283</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19494,8 +19504,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19538,7 +19553,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 32130-2026</t>
+          <t>A 40339-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19552,10 +19567,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46234</v>
+        <v>45555</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19568,7 +19583,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19611,7 +19626,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38209-2026</t>
+          <t>A 9754-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19625,10 +19640,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46281</v>
+        <v>44618</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19640,13 +19655,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19689,7 +19699,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 33887-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19703,10 +19713,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45638</v>
+        <v>45523</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19719,7 +19729,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19762,7 +19772,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 32432-2026</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19776,10 +19786,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46239</v>
+        <v>45147</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19791,13 +19801,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19840,7 +19845,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 4977-2023</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19854,10 +19859,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44958</v>
+        <v>44677</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19870,7 +19875,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19913,7 +19918,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 33887-2024</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19927,10 +19932,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45523</v>
+        <v>44791</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19943,7 +19948,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19986,7 +19991,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38673-2026</t>
+          <t>A 40527-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20000,10 +20005,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20021,7 +20026,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20064,7 +20069,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 29112-2023</t>
+          <t>A 40570-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20078,10 +20083,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45105</v>
+        <v>46295</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20093,8 +20098,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20137,7 +20147,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20151,10 +20161,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45461</v>
+        <v>45225</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20167,7 +20177,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20210,7 +20220,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20224,10 +20234,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45182</v>
+        <v>45104</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20240,7 +20250,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.8</v>
+        <v>6.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20283,7 +20293,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 45229-2023</t>
+          <t>A 40528-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20297,10 +20307,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45191</v>
+        <v>46295</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20312,8 +20322,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20356,7 +20371,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 60397-2022</t>
+          <t>A 40335-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20370,10 +20385,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44910</v>
+        <v>46294</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20385,8 +20400,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20429,7 +20449,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 11631-2022</t>
+          <t>A 40459-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20443,10 +20463,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44631</v>
+        <v>46294</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20458,13 +20478,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20507,7 +20522,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 8936-2025</t>
+          <t>A 40525-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20521,10 +20536,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45714</v>
+        <v>46295</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20536,8 +20551,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20580,7 +20600,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 38676-2026</t>
+          <t>A 40532-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20594,10 +20614,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20615,7 +20635,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20658,7 +20678,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 38674-2026</t>
+          <t>A 40533-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20672,10 +20692,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20693,7 +20713,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20736,7 +20756,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 27767-2023</t>
+          <t>A 40336-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20750,10 +20770,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45098</v>
+        <v>46294</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20765,8 +20785,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20809,7 +20834,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 62217-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20819,14 +20844,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45388</v>
+        <v>45267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20839,7 +20864,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20882,7 +20907,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 34116-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20896,10 +20921,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45279</v>
+        <v>46253</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20911,13 +20936,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20960,7 +20980,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20974,10 +20994,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45252</v>
+        <v>44493</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20990,7 +21010,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21033,7 +21053,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21047,10 +21067,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45636</v>
+        <v>45370</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21062,8 +21082,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21106,7 +21131,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 9754-2022</t>
+          <t>A 8295-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21120,10 +21145,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44618</v>
+        <v>45352</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21136,7 +21161,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21179,7 +21204,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 40336-2026</t>
+          <t>A 24832-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21193,10 +21218,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46294</v>
+        <v>45461</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21208,13 +21233,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21257,7 +21277,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 40335-2026</t>
+          <t>A 33145-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -21271,10 +21291,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46294</v>
+        <v>46245</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21286,13 +21306,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -21335,7 +21350,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 2413-2024</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -21349,10 +21364,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45310</v>
+        <v>44534</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21365,7 +21380,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -21408,7 +21423,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 34116-2026</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -21422,10 +21437,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46253</v>
+        <v>45070</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21438,7 +21453,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -21481,7 +21496,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 40525-2026</t>
+          <t>A 11631-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -21495,10 +21510,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46295</v>
+        <v>44631</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21516,7 +21531,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -21559,7 +21574,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 40532-2026</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -21569,14 +21584,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46295</v>
+        <v>44593</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21590,11 +21605,11 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.9</v>
+        <v>38.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -21637,7 +21652,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 40533-2026</t>
+          <t>A 37849-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -21651,10 +21666,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46295</v>
+        <v>45158</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21666,13 +21681,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21715,7 +21725,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 40459-2026</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21729,10 +21739,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46294</v>
+        <v>45457</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21745,7 +21755,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21788,7 +21798,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 40528-2026</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21802,10 +21812,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46295</v>
+        <v>45457</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21817,13 +21827,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21866,7 +21871,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 40570-2026</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21880,10 +21885,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46295</v>
+        <v>45145</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21895,13 +21900,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21944,7 +21944,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 16281-2024</t>
+          <t>A 73009-2021</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21958,10 +21958,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45407</v>
+        <v>44550</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21973,8 +21973,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -22017,7 +22022,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 40527-2026</t>
+          <t>A 8936-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -22031,10 +22036,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46295</v>
+        <v>45714</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22046,13 +22051,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -22095,7 +22095,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 16281-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -22109,10 +22109,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45670</v>
+        <v>45407</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -22168,7 +22168,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 33145-2026</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -22182,10 +22182,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46245</v>
+        <v>45670</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -22258,7 +22258,7 @@
         <v>45617</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45414</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44904</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>45953</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45278</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46111</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>46036</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45090</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45937</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45775</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45866</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44807</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44714</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44791</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45389</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45414</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45406</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45638</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44879</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44958</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>45406</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45461</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44481</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45104</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45258</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44631</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45098</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45388</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44834</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45370</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45015</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45252</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45457</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44862</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44618</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44534</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44493</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45310</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45461</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45246</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45384</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45408</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44593</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44550</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45414</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44957</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45145</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45555</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44593</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45364</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44859</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45158</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45226</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45608</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45453</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45825</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44677</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45939</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45317</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45215</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45149</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45714</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45198</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44682</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45457</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45457</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45740</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45166</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44791</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45758</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45461</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45184</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45849</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45267</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45091</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45161</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44845</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45555</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>46099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45091</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45070</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45985</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45208</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>46107</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45461</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46113</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44791</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46134</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>46134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46134</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46134</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45224</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>44960</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45147</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45729</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45461</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45266</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46147</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46147</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46147</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46147</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46154</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>46155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45526</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>46155</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>46155</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46155</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>46155</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>46177</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45995</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46211</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>46211</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46211</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46211</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46265</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46265</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46265</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46265</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>46265</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>46224</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46224</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>46276</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>46279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>46234</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>46281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46283</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46283</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46294</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46294</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>46253</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46295</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>46295</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>46295</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46294</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46295</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46295</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46295</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>46245</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46302</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>46303</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46302</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44904</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46089</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45980</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46111</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>44620</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46253</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45840</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>45978</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>46013</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45978</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45960</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45278</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46111</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>46036</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45090</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45400</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45219</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45937</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45741</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45741</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45775</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45510</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45866</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>46210</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44807</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44714</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44791</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45196</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45389</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45414</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45406</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45091</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45638</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44879</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>44958</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>45406</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45105</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45461</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45182</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44481</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45104</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45258</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44631</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45098</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45388</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44834</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45370</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45015</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45352</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45252</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45457</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44818</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44862</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45279</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44618</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44534</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44493</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45310</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45461</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45246</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45384</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45408</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45231</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45670</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44593</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44550</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45414</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44957</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45145</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45555</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45187</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44593</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45364</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44859</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45158</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45226</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45608</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>45453</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         <v>45825</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>44677</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45939</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45317</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45215</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45149</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45714</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45198</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45947</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45714</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44682</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45457</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45457</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45740</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45166</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44791</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45758</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45461</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45184</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45147</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45849</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45267</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>44503</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45091</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45161</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44845</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45596</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45755</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45555</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>46099</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45091</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45070</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45985</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>44896</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45208</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>46107</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45461</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46113</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>46113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>46113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45994</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44791</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46134</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>46134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>46134</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>46134</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45224</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>44960</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45147</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>46034</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>46043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45729</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45461</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45266</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46147</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46147</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46147</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46147</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46154</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>46155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45526</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>46155</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>46155</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46155</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>46155</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>46155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>46177</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45995</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46211</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>46211</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46211</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45901</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46211</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46265</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20375,7 +20375,7 @@
         <v>46265</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>46265</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46265</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>46265</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>46224</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>46224</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>46276</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>46279</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>46234</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>46281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46283</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>46283</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46283</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46294</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46294</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>46253</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46295</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>46295</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>46295</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46294</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46295</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46295</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46295</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>46245</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>46302</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>46303</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46302</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44904</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46089</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>46307</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46111</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>46253</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44495</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45910</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>44529</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44868</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44862</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44707</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45278</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>46036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44593</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45775</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>46294</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45400</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45316</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44560</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44807</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44714</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44530</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44958</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>44791</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45231</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45406</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45388</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45457</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45166</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45258</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44818</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45406</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45636</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45198</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45384</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45729</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45252</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44862</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45317</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45196</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45149</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>46147</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45191</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45364</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45939</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45939</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>46155</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>46155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46155</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45526</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45755</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45953</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46154</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>46155</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45208</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45740</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45985</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45555</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45098</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45389</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45461</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44879</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45414</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46034</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45408</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>46177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44682</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45091</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45015</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45758</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>46107</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45555</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>46113</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>46113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44618</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45523</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>46134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46134</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>46134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>46134</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>46134</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45147</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44677</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44791</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>45225</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>46211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>46211</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45901</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45267</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>46224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46224</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44493</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45352</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45461</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46234</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44534</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>46279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>46276</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>46281</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44631</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46239</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46283</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>46283</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>46283</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44593</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45158</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45457</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45457</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45145</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44550</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46295</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>46295</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46294</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>46294</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>46295</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45714</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>46294</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>46253</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>46245</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>46302</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45407</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46302</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45670</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>46302</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45617</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>46303</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>45414</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46265</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>46265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>46309</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>46309</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45608</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45453</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>46268</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45849</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45596</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44904</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46089</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>46307</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46111</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>46253</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46269</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44495</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45910</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>44529</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45891</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>44868</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44862</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44707</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45408</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45278</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>46036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45978</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46111</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>44593</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45775</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45866</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45027</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>46294</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45400</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45316</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>45775</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>44876</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>44799</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44560</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44807</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44687</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44714</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44841</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44530</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44958</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>44791</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>45191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45231</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45266</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45406</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45388</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45457</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45226</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45166</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45258</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>45461</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44818</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45406</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45279</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45636</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45198</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45384</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44960</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45532</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45729</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45252</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44862</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45317</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45196</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45149</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>46147</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>46147</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>46147</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46147</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>46147</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45279</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45191</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45364</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>45825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45929</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45939</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45939</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>46155</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>46155</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>46155</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13028,7 +13028,7 @@
         <v>45246</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45526</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45755</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45953</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46154</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>46155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>46155</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45208</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44791</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45740</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45985</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>44845</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45555</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45098</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45994</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45994</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45389</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45461</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44879</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45414</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46034</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45408</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>46043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>46177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44682</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45091</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45015</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45758</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>46099</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46099</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>46107</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45555</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46107</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46107</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45995</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>46113</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>46113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44618</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45523</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>46134</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46134</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>46134</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46134</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>46134</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>46134</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>46134</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>46134</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45147</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44677</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>44791</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>45225</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>46211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>46211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>46211</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45901</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46211</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45267</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>46224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46224</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44493</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45352</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45461</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46234</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44534</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>46279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>46276</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>46281</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44631</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46239</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46283</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>46283</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>46283</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44593</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45158</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45457</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45457</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45145</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44550</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46295</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>46295</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46294</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>46294</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>46295</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>46295</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>46295</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45714</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>46294</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>46253</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>46245</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>46302</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45407</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46302</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45670</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>46302</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45617</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>46303</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>45414</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46265</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>46265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>46309</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>46309</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45608</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45453</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>46268</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45849</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45596</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44904</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46089</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>

--- a/Översikt NORA.xlsx
+++ b/Översikt NORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE271"/>
+  <dimension ref="A1:AE273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46195</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>46013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>44841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>46307</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46111</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45623</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>46253</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56956-2025</t>
+          <t>A 33136-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45978</v>
+        <v>45840</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2494,17 +2494,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>22.2</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -2531,12 +2531,131 @@
         <v>6</v>
       </c>
       <c r="T17" t="n">
+        <v>8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp
+Tallticka
+Smal svampklubba
+Spillkråka
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 56956-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
         <v>15</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>15</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tretåig hackspett
@@ -2546,155 +2665,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 56956-2025 artfynd.xlsx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 56956-2025 karta.png", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 56956-2025 georefererad karta.tif", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 56956-2025 FSC-klagomål.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 56956-2025 FSC-klagomål mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 56956-2025 tillsynsbegäran.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 56956-2025 tillsynsbegäran mail.docx", "A 56956-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 56956-2025 prioriterade fågelarter.docx", "A 56956-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 33136-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45840</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp
-Tallticka
-Smal svampklubba
-Spillkråka
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 33136-2025 artfynd.xlsx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 33136-2025 karta.png", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 33136-2025 georefererad karta.tif", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 33136-2025 FSC-klagomål.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 33136-2025 FSC-klagomål mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 33136-2025 tillsynsbegäran.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 33136-2025 tillsynsbegäran mail.docx", "A 33136-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 33136-2025 prioriterade fågelarter.docx", "A 33136-2025")</f>
         <v/>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
         <v>46269</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44495</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46013</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45978</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45910</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>44529</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39837-2025</t>
+          <t>A 51036-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45891</v>
+        <v>44868</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3453,149 +3453,149 @@
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Loppstarr
+Vårärt
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 39837-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45891</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bårdlav
 Stuplav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 39837-2025 artfynd.xlsx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 39837-2025 karta.png", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 39837-2025 georefererad karta.tif", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 39837-2025 FSC-klagomål.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 39837-2025 FSC-klagomål mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 39837-2025 tillsynsbegäran.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 39837-2025 tillsynsbegäran mail.docx", "A 39837-2025")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 39837-2025 prioriterade fågelarter.docx", "A 39837-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 51036-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44868</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NORA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Loppstarr
-Vårärt
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 51036-2022 artfynd.xlsx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 51036-2022 karta.png", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 51036-2022 georefererad karta.tif", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 51036-2022 FSC-klagomål.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 51036-2022 FSC-klagomål mail.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 51036-2022 tillsynsbegäran.docx", "A 51036-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 51036-2022 tillsynsbegäran mail.docx", "A 51036-2022")</f>
         <v/>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44707</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45408</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45408</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45978</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>46111</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45278</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45702</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44593</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20565-2025</t>
+          <t>A 15327-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45775</v>
+        <v>45400</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5188,13 +5188,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5230,46 +5225,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15327-2024</t>
+          <t>A 48775-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45400</v>
+        <v>45937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5299,16 +5294,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5323,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5339,42 +5334,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 15327-2024 artfynd.xlsx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 15327-2024 karta.png", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 15327-2024 georefererad karta.tif", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 15327-2024 FSC-klagomål.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 15327-2024 FSC-klagomål mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 15327-2024 tillsynsbegäran.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 15327-2024 tillsynsbegäran mail.docx", "A 15327-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48775-2025</t>
+          <t>A 14477-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5384,14 +5379,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45937</v>
+        <v>45741</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5403,24 +5398,29 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5444,42 +5444,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattmynta</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 48775-2025 artfynd.xlsx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 48775-2025 karta.png", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 48775-2025 georefererad karta.tif", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 48775-2025 FSC-klagomål.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 48775-2025 FSC-klagomål mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 48775-2025 tillsynsbegäran.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 48775-2025 tillsynsbegäran mail.docx", "A 48775-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25723-2023</t>
+          <t>A 14482-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5489,14 +5489,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45090</v>
+        <v>45741</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,8 +5508,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5518,13 +5523,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5536,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5545,46 +5550,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53129-2023</t>
+          <t>A 42049-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5594,14 +5599,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45229</v>
+        <v>45177</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,8 +5618,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5650,46 +5660,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14477-2025</t>
+          <t>A 16063-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5699,14 +5709,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45741</v>
+        <v>45027</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,28 +5728,23 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5760,46 +5765,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Kattmynta</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14477-2025 artfynd.xlsx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14477-2025 karta.png", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14477-2025 georefererad karta.tif", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14477-2025 FSC-klagomål.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14477-2025 FSC-klagomål mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14477-2025 tillsynsbegäran.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14477-2025 tillsynsbegäran mail.docx", "A 14477-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14482-2025</t>
+          <t>A 36089-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5809,14 +5814,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45741</v>
+        <v>45866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5828,16 +5833,11 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5870,46 +5870,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Flodpärlmussla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 14482-2025 artfynd.xlsx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 14482-2025 karta.png", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 14482-2025 georefererad karta.tif", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 14482-2025 FSC-klagomål.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 14482-2025 FSC-klagomål mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 14482-2025 tillsynsbegäran.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 14482-2025 tillsynsbegäran mail.docx", "A 14482-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36089-2025</t>
+          <t>A 52639-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45866</v>
+        <v>45219</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5938,8 +5938,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -5948,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5963,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5975,46 +5980,50 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 36089-2025 artfynd.xlsx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 36089-2025 karta.png", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 36089-2025 georefererad karta.tif", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 36089-2025 FSC-klagomål.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 36089-2025 FSC-klagomål mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 36089-2025 tillsynsbegäran.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 36089-2025 tillsynsbegäran mail.docx", "A 36089-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
+        <v/>
+      </c>
+      <c r="AE48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42049-2023</t>
+          <t>A 20565-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6028,10 +6037,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45177</v>
+        <v>45775</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6049,7 +6058,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6089,42 +6098,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 42049-2023 artfynd.xlsx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 20565-2025 artfynd.xlsx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 42049-2023 karta.png", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 20565-2025 karta.png", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 42049-2023 georefererad karta.tif", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 20565-2025 georefererad karta.tif", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 42049-2023 FSC-klagomål.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 20565-2025 FSC-klagomål.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 42049-2023 FSC-klagomål mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 20565-2025 FSC-klagomål mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 42049-2023 tillsynsbegäran.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 20565-2025 tillsynsbegäran.docx", "A 20565-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 42049-2023 tillsynsbegäran mail.docx", "A 42049-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 20565-2025 tillsynsbegäran mail.docx", "A 20565-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30586-2026</t>
+          <t>A 53129-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6138,10 +6147,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46210</v>
+        <v>45229</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6154,7 +6163,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6163,13 +6172,13 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6181,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6194,42 +6203,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 53129-2023 artfynd.xlsx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 53129-2023 karta.png", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 53129-2023 georefererad karta.tif", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 53129-2023 FSC-klagomål.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 53129-2023 FSC-klagomål mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 53129-2023 tillsynsbegäran.docx", "A 53129-2023")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 53129-2023 tillsynsbegäran mail.docx", "A 53129-2023")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31957-2024</t>
+          <t>A 30586-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6243,10 +6252,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45510</v>
+        <v>46210</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6259,23 +6268,23 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
@@ -6283,10 +6292,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6295,46 +6304,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 30586-2026 artfynd.xlsx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 30586-2026 karta.png", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 30586-2026 georefererad karta.tif", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 30586-2026 FSC-klagomål.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 30586-2026 FSC-klagomål mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 30586-2026 tillsynsbegäran.docx", "A 30586-2026")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 30586-2026 tillsynsbegäran mail.docx", "A 30586-2026")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52639-2023</t>
+          <t>A 31957-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6348,10 +6357,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45219</v>
+        <v>45510</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6363,13 +6372,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6378,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -6393,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -6409,46 +6413,42 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 52639-2023 artfynd.xlsx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 31957-2024 artfynd.xlsx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 52639-2023 karta.png", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 31957-2024 karta.png", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 52639-2023 georefererad karta.tif", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 31957-2024 georefererad karta.tif", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 52639-2023 FSC-klagomål.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 31957-2024 FSC-klagomål.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 52639-2023 FSC-klagomål mail.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 31957-2024 FSC-klagomål mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 52639-2023 tillsynsbegäran.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 31957-2024 tillsynsbegäran.docx", "A 31957-2024")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 52639-2023 tillsynsbegäran mail.docx", "A 52639-2023")</f>
-        <v/>
-      </c>
-      <c r="AE52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/fåglar/A 52639-2023 prioriterade fågelarter.docx", "A 52639-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 31957-2024 tillsynsbegäran mail.docx", "A 31957-2024")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16063-2023</t>
+          <t>A 25723-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45027</v>
+        <v>45090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6514,39 +6514,39 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 16063-2023 artfynd.xlsx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/artfynd/A 25723-2023 artfynd.xlsx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 16063-2023 karta.png", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor/A 25723-2023 karta.png", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 16063-2023 georefererad karta.tif", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/kartor_geotiff/A 25723-2023 georefererad karta.tif", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 16063-2023 FSC-klagomål.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomål/A 25723-2023 FSC-klagomål.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 16063-2023 FSC-klagomål mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/klagomålsmail/A 25723-2023 FSC-klagomål mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 16063-2023 tillsynsbegäran.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsyn/A 25723-2023 tillsynsbegäran.docx", "A 25723-2023")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 16063-2023 tillsynsbegäran mail.docx", "A 16063-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1884/tillsynsmail/A 25723-2023 tillsynsbegäran mail.docx", "A 25723-2023")</f>
         <v/>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
         <v>46294</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45775</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44876</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44761</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44807</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44687</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44714</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44841</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44491</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44530</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62592-2021</t>
+          <t>A 34026-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44503</v>
+        <v>44791</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4910-2023</t>
+          <t>A 43254-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44958</v>
+        <v>44834</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34164-2022</t>
+          <t>A 46198-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44791</v>
+        <v>45196</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8369,13 +8369,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8418,7 +8413,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45216-2023</t>
+          <t>A 16109-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45191</v>
+        <v>45406</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8448,7 +8443,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8491,7 +8486,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26023-2023</t>
+          <t>A 13585-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8501,14 +8496,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45091</v>
+        <v>45389</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8520,13 +8515,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8569,7 +8559,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61952-2023</t>
+          <t>A 53472-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8579,14 +8569,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45266</v>
+        <v>44879</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8599,7 +8589,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8642,7 +8632,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1566-2025</t>
+          <t>A 26021-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8656,10 +8646,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45670</v>
+        <v>45091</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8671,8 +8661,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8715,7 +8710,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 54604-2024</t>
+          <t>A 4910-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8729,10 +8724,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45617</v>
+        <v>44958</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8745,7 +8740,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8788,7 +8783,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53938-2023</t>
+          <t>A 1566-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8802,10 +8797,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45231</v>
+        <v>45670</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8818,7 +8813,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8861,7 +8856,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49632-2022</t>
+          <t>A 54604-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8875,10 +8870,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44862</v>
+        <v>45617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8890,13 +8885,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8939,7 +8929,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13563-2024</t>
+          <t>A 17344-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8949,14 +8939,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45388</v>
+        <v>45414</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8969,7 +8959,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9012,7 +9002,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16085-2024</t>
+          <t>A 24389-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9026,10 +9016,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45406</v>
+        <v>45457</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9042,7 +9032,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9085,7 +9075,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17344-2024</t>
+          <t>A 49632-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9099,10 +9089,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45414</v>
+        <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9114,8 +9104,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9158,7 +9153,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24389-2024</t>
+          <t>A 64089-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45457</v>
+        <v>45279</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9187,8 +9182,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52879-2023</t>
+          <t>A 70200-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9245,10 +9245,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45226</v>
+        <v>44534</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9457-2025</t>
+          <t>A 59637-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45714</v>
+        <v>44493</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9377,7 +9377,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38179-2023</t>
+          <t>A 42056-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9391,10 +9391,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45161</v>
+        <v>45903</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
         <v>45608</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23277-2024</t>
+          <t>A 56136-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45453</v>
+        <v>44889</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9596,7 +9596,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43535-2023</t>
+          <t>A 23277-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9610,10 +9610,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45184</v>
+        <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9669,7 +9669,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35675-2023</t>
+          <t>A 16557-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45147</v>
+        <v>45408</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9698,8 +9698,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9742,7 +9747,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39257-2023</t>
+          <t>A 53938-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9756,10 +9761,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45166</v>
+        <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9772,7 +9777,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9815,7 +9820,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59607-2024</t>
+          <t>A 5217-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9825,14 +9830,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45638</v>
+        <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9844,8 +9849,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>38.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9888,7 +9898,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42056-2025</t>
+          <t>A 29669-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9902,10 +9912,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45903</v>
+        <v>45825</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9918,7 +9928,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9961,7 +9971,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1766-2026</t>
+          <t>A 34835-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9975,10 +9985,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46034</v>
+        <v>45849</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9990,8 +10000,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10034,7 +10049,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60301-2023</t>
+          <t>A 4723-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10048,10 +10063,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45258</v>
+        <v>44957</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10064,7 +10079,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10107,7 +10122,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3686-2026</t>
+          <t>A 35144-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10121,10 +10136,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46043</v>
+        <v>45145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10137,7 +10152,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10180,7 +10195,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26021-2023</t>
+          <t>A 1766-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10194,10 +10209,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45091</v>
+        <v>46034</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10209,13 +10224,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10258,7 +10268,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24820-2024</t>
+          <t>A 49671-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10268,14 +10278,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45461</v>
+        <v>45939</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10288,7 +10298,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10331,7 +10341,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39707-2022</t>
+          <t>A 51002-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10345,10 +10355,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44818</v>
+        <v>45947</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10360,13 +10370,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10409,7 +10414,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24821-2024</t>
+          <t>A 5049-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10423,10 +10428,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45461</v>
+        <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10439,7 +10444,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>12.2</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10482,7 +10487,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16109-2024</t>
+          <t>A 52380-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10492,14 +10497,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45406</v>
+        <v>45953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10511,8 +10516,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10555,7 +10565,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10441-2026</t>
+          <t>A 49498-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10569,10 +10579,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46076</v>
+        <v>45596</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10586,11 +10596,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10633,7 +10643,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57316-2022</t>
+          <t>A 10079-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10643,14 +10653,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44896</v>
+        <v>45364</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10711,7 +10721,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43843-2023</t>
+          <t>A 48707-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10721,14 +10731,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45187</v>
+        <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10740,13 +10750,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10789,7 +10794,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43919-2023</t>
+          <t>A 45159-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10803,10 +10808,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45182</v>
+        <v>45191</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10819,7 +10824,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10862,7 +10867,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29669-2025</t>
+          <t>A 52879-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10876,10 +10881,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45825</v>
+        <v>45226</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10892,7 +10897,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10935,7 +10940,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49671-2025</t>
+          <t>A 54595-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10945,14 +10950,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45939</v>
+        <v>45965</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10965,7 +10970,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11008,7 +11013,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51002-2025</t>
+          <t>A 45216-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11022,10 +11027,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45947</v>
+        <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11038,7 +11043,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11081,7 +11086,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 64090-2023</t>
+          <t>A 17140-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11095,10 +11100,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45279</v>
+        <v>44677</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11110,13 +11115,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11159,7 +11159,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52380-2025</t>
+          <t>A 3686-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11169,14 +11169,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45953</v>
+        <v>46043</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11188,13 +11188,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11237,7 +11232,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14242-2026</t>
+          <t>A 3309-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11251,10 +11246,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46099</v>
+        <v>45317</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11267,7 +11262,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11310,7 +11305,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5049-2022</t>
+          <t>A 9295-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11324,10 +11319,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44593</v>
+        <v>45714</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11340,7 +11335,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11383,7 +11378,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59056-2024</t>
+          <t>A 58521-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11397,10 +11392,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45636</v>
+        <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11413,7 +11408,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11456,7 +11451,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 14253-2026</t>
+          <t>A 60152-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11470,10 +11465,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46099</v>
+        <v>45994</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11486,7 +11481,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11529,7 +11524,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9295-2025</t>
+          <t>A 60166-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11543,10 +11538,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45714</v>
+        <v>45994</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11559,7 +11554,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11602,7 +11597,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4723-2023</t>
+          <t>A 24391-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11616,10 +11611,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44957</v>
+        <v>45457</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11632,7 +11627,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11675,7 +11670,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15712-2026</t>
+          <t>A 24392-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11689,10 +11684,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46107</v>
+        <v>45457</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11705,7 +11700,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11748,7 +11743,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15692-2026</t>
+          <t>A 14315-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11762,10 +11757,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46107</v>
+        <v>45740</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11778,7 +11773,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11821,7 +11816,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15702-2026</t>
+          <t>A 34206-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11835,10 +11830,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46107</v>
+        <v>44791</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11850,8 +11845,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11894,7 +11894,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54595-2025</t>
+          <t>A 17716-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45965</v>
+        <v>45758</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11967,7 +11967,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 16813-2026</t>
+          <t>A 43535-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11981,10 +11981,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46113</v>
+        <v>45184</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11996,13 +11996,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12045,7 +12040,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16815-2026</t>
+          <t>A 35659-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12059,10 +12054,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46113</v>
+        <v>45147</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12074,13 +12069,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12123,7 +12113,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16816-2026</t>
+          <t>A 52505-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12137,10 +12127,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46113</v>
+        <v>45225</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12152,13 +12142,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12201,7 +12186,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46688-2023</t>
+          <t>A 26022-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12215,10 +12200,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45198</v>
+        <v>45091</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12230,8 +12215,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12274,7 +12264,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 16808-2026</t>
+          <t>A 38179-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12288,10 +12278,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46113</v>
+        <v>45161</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12303,13 +12293,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12352,7 +12337,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16814-2026</t>
+          <t>A 10441-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12366,10 +12351,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46113</v>
+        <v>46076</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12383,11 +12368,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12430,7 +12415,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16811-2026</t>
+          <t>A 45645-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12444,10 +12429,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46113</v>
+        <v>44845</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12457,11 +12442,6 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -12508,7 +12488,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 12646-2024</t>
+          <t>A 40497-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12522,10 +12502,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45384</v>
+        <v>45555</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12538,7 +12518,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12581,7 +12561,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24822-2024</t>
+          <t>A 22389-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12595,10 +12575,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45461</v>
+        <v>45070</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12611,7 +12591,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12654,7 +12634,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19501-2026</t>
+          <t>A 14242-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12668,10 +12648,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12683,13 +12663,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12732,7 +12707,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 19503-2026</t>
+          <t>A 14253-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12746,10 +12721,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12761,13 +12736,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12810,7 +12780,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19510-2026</t>
+          <t>A 15702-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12824,10 +12794,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46134</v>
+        <v>46107</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12839,13 +12809,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12888,7 +12853,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 19512-2026</t>
+          <t>A 15712-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12902,10 +12867,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46134</v>
+        <v>46107</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12915,11 +12880,6 @@
       <c r="G137" t="inlineStr">
         <is>
           <t>NORA</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -12966,7 +12926,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19502-2026</t>
+          <t>A 15692-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12980,10 +12940,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46134</v>
+        <v>46107</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12995,13 +12955,8 @@
           <t>NORA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13044,7 +12999,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 19504-2026</t>
+          <t>A 16813-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13058,10 +13013,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13079,7 +13034,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13122,7 +13077,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 19505-2026</t>
+          <t>A 16815-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13136,10 +13091,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13157,7 +13112,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13200,7 +13155,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19509-2026</t>
+          <t>A 16816-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13214,10 +13169,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13235,7 +13190,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13278,7 +13233,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5674-2023</t>
+          <t>A 16811-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13292,10 +13247,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44960</v>
+        <v>46113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13309,11 +13264,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13356,7 +13311,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19553-2026</t>
+          <t>A 16808-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13370,10 +13325,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13391,7 +13346,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13434,7 +13389,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58521-2025</t>
+          <t>A 16085-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13448,10 +13403,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45985</v>
+        <v>45406</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13464,7 +13419,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13507,7 +13462,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34835-2025</t>
+          <t>A 16814-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13521,10 +13476,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45849</v>
+        <v>46113</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13542,7 +13497,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13585,7 +13540,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 45159-2023</t>
+          <t>A 29018-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13599,10 +13554,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45191</v>
+        <v>45104</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13615,7 +13570,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13658,7 +13613,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 60152-2025</t>
+          <t>A 60301-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13672,10 +13627,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45994</v>
+        <v>45258</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13688,7 +13643,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13731,7 +13686,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60166-2025</t>
+          <t>A 38177-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13745,10 +13700,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45994</v>
+        <v>45161</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13761,7 +13716,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13804,7 +13759,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58829-2023</t>
+          <t>A 19501-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13818,10 +13773,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45252</v>
+        <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13833,8 +13788,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13877,7 +13837,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 3309-2024</t>
+          <t>A 19503-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13891,10 +13851,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45317</v>
+        <v>46134</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13906,8 +13866,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13950,7 +13915,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 46198-2023</t>
+          <t>A 10882-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13964,10 +13929,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45196</v>
+        <v>45370</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13979,8 +13944,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14023,7 +13993,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 36064-2023</t>
+          <t>A 19502-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14037,10 +14007,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45149</v>
+        <v>46134</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14050,6 +14020,11 @@
       <c r="G152" t="inlineStr">
         <is>
           <t>NORA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -14096,7 +14071,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35656-2024</t>
+          <t>A 19504-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14106,14 +14081,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45532</v>
+        <v>46134</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14125,8 +14100,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14169,7 +14149,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 43254-2022</t>
+          <t>A 19505-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14183,10 +14163,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44834</v>
+        <v>46134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14198,8 +14178,13 @@
           <t>NORA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</